--- a/research/traditional_assets/database/data/switzerland/switzerland_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_real_estate_development.xlsx
@@ -1398,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1535,22 +1535,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06510040018055782</v>
+        <v>0.0650437835962942</v>
       </c>
       <c r="C2">
-        <v>404.2837832398469</v>
+        <v>401.3713869336797</v>
       </c>
       <c r="D2">
-        <v>399.2437832398469</v>
+        <v>400.4183869336796</v>
       </c>
       <c r="E2">
-        <v>-19.7</v>
+        <v>-15.613</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.087</v>
       </c>
       <c r="G2">
         <v>5.04</v>
@@ -1571,28 +1571,28 @@
         <v>7.46</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2055761</v>
       </c>
       <c r="N2">
-        <v>7.46</v>
+        <v>7.2544239</v>
       </c>
       <c r="O2">
-        <v>1.08916</v>
+        <v>1.0591458894</v>
       </c>
       <c r="P2">
-        <v>6.37084</v>
+        <v>6.1952780106</v>
       </c>
       <c r="Q2">
-        <v>-1.08916</v>
+        <v>-1.2647219894</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06510040018055782</v>
+        <v>0.06526689050130728</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241993</v>
+        <v>0.4495817667738403</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>36.28826502691704</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1617,22 +1617,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0650437835962942</v>
+        <v>0.06498716701203061</v>
       </c>
       <c r="C3">
-        <v>401.3713869336797</v>
+        <v>398.4659225574801</v>
       </c>
       <c r="D3">
-        <v>400.4183869336796</v>
+        <v>401.5999225574801</v>
       </c>
       <c r="E3">
-        <v>-15.613</v>
+        <v>-11.526</v>
       </c>
       <c r="F3">
-        <v>4.087</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="G3">
         <v>5.04</v>
@@ -1653,28 +1653,28 @@
         <v>7.46</v>
       </c>
       <c r="M3">
-        <v>0.2055761</v>
+        <v>0.4111522</v>
       </c>
       <c r="N3">
-        <v>7.2544239</v>
+        <v>7.0488478</v>
       </c>
       <c r="O3">
-        <v>1.0591458894</v>
+        <v>1.0291317788</v>
       </c>
       <c r="P3">
-        <v>6.1952780106</v>
+        <v>6.0197160212</v>
       </c>
       <c r="Q3">
-        <v>-1.2647219894</v>
+        <v>-1.4402839788</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06526689050130728</v>
+        <v>0.0654367785837047</v>
       </c>
       <c r="T3">
-        <v>0.4495817667738403</v>
+        <v>0.4535052790693924</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>36.28826502691704</v>
+        <v>18.14413251345852</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1699,22 +1699,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06498716701203061</v>
+        <v>0.06496898042776698</v>
       </c>
       <c r="C4">
-        <v>398.4659225574801</v>
+        <v>394.759940779048</v>
       </c>
       <c r="D4">
-        <v>401.5999225574801</v>
+        <v>401.980940779048</v>
       </c>
       <c r="E4">
-        <v>-11.526</v>
+        <v>-7.439</v>
       </c>
       <c r="F4">
-        <v>8.173999999999999</v>
+        <v>12.261</v>
       </c>
       <c r="G4">
         <v>5.04</v>
@@ -1735,45 +1735,45 @@
         <v>7.46</v>
       </c>
       <c r="M4">
-        <v>0.4111522</v>
+        <v>0.6351197999999999</v>
       </c>
       <c r="N4">
-        <v>7.0488478</v>
+        <v>6.8248802</v>
       </c>
       <c r="O4">
-        <v>1.0291317788</v>
+        <v>0.9964325091999999</v>
       </c>
       <c r="P4">
-        <v>6.0197160212</v>
+        <v>5.8284476908</v>
       </c>
       <c r="Q4">
-        <v>-1.4402839788</v>
+        <v>-1.6315523092</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0654367785837047</v>
+        <v>0.06561016951316184</v>
       </c>
       <c r="T4">
-        <v>0.4535052790693924</v>
+        <v>0.4575096885256776</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>18.14413251345852</v>
+        <v>11.74581551386054</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1781,22 +1781,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06496898042776698</v>
+        <v>0.06498324584350337</v>
       </c>
       <c r="C5">
-        <v>394.759940779048</v>
+        <v>390.3740119489063</v>
       </c>
       <c r="D5">
-        <v>401.980940779048</v>
+        <v>401.6820119489063</v>
       </c>
       <c r="E5">
-        <v>-7.439</v>
+        <v>-3.352</v>
       </c>
       <c r="F5">
-        <v>12.261</v>
+        <v>16.348</v>
       </c>
       <c r="G5">
         <v>5.04</v>
@@ -1817,45 +1817,45 @@
         <v>7.46</v>
       </c>
       <c r="M5">
-        <v>0.6351197999999999</v>
+        <v>0.8746179999999999</v>
       </c>
       <c r="N5">
-        <v>6.8248802</v>
+        <v>6.585382</v>
       </c>
       <c r="O5">
-        <v>0.9964325091999999</v>
+        <v>0.9614657719999999</v>
       </c>
       <c r="P5">
-        <v>5.8284476908</v>
+        <v>5.623916228000001</v>
       </c>
       <c r="Q5">
-        <v>-1.6315523092</v>
+        <v>-1.836083771999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06561016951316184</v>
+        <v>0.06578717275364934</v>
       </c>
       <c r="T5">
-        <v>0.4575096885256776</v>
+        <v>0.4615975231789687</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>11.74581551386054</v>
+        <v>8.529437994644521</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1863,22 +1863,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06498324584350337</v>
+        <v>0.06498811725923975</v>
       </c>
       <c r="C6">
-        <v>390.3740119489063</v>
+        <v>386.1850342484581</v>
       </c>
       <c r="D6">
-        <v>401.6820119489063</v>
+        <v>401.5800342484581</v>
       </c>
       <c r="E6">
-        <v>-3.352</v>
+        <v>0.735000000000003</v>
       </c>
       <c r="F6">
-        <v>16.348</v>
+        <v>20.435</v>
       </c>
       <c r="G6">
         <v>5.04</v>
@@ -1899,45 +1899,45 @@
         <v>7.46</v>
       </c>
       <c r="M6">
-        <v>0.8746179999999999</v>
+        <v>1.1096205</v>
       </c>
       <c r="N6">
-        <v>6.585382</v>
+        <v>6.3503795</v>
       </c>
       <c r="O6">
-        <v>0.9614657719999999</v>
+        <v>0.9271554069999999</v>
       </c>
       <c r="P6">
-        <v>5.623916228000001</v>
+        <v>5.423224093</v>
       </c>
       <c r="Q6">
-        <v>-1.836083771999999</v>
+        <v>-2.036775907</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06578717275364934</v>
+        <v>0.06596790237814712</v>
       </c>
       <c r="T6">
-        <v>0.4615975231789687</v>
+        <v>0.4657714175091712</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.529437994644521</v>
+        <v>6.723019266496968</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1945,22 +1945,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06498811725923975</v>
+        <v>0.06501690067497615</v>
       </c>
       <c r="C7">
-        <v>386.1850342484581</v>
+        <v>381.496540528284</v>
       </c>
       <c r="D7">
-        <v>401.5800342484581</v>
+        <v>400.9785405282839</v>
       </c>
       <c r="E7">
-        <v>0.735000000000003</v>
+        <v>4.822000000000003</v>
       </c>
       <c r="F7">
-        <v>20.435</v>
+        <v>24.522</v>
       </c>
       <c r="G7">
         <v>5.04</v>
@@ -1981,45 +1981,45 @@
         <v>7.46</v>
       </c>
       <c r="M7">
-        <v>1.1096205</v>
+        <v>1.3560666</v>
       </c>
       <c r="N7">
-        <v>6.3503795</v>
+        <v>6.1039334</v>
       </c>
       <c r="O7">
-        <v>0.9271554069999999</v>
+        <v>0.8911742763999999</v>
       </c>
       <c r="P7">
-        <v>5.423224093</v>
+        <v>5.2127591236</v>
       </c>
       <c r="Q7">
-        <v>-2.036775907</v>
+        <v>-2.2472408764</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06596790237814712</v>
+        <v>0.06615247731380441</v>
       </c>
       <c r="T7">
-        <v>0.4657714175091712</v>
+        <v>0.4700341181017184</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.723019266496968</v>
+        <v>5.501204734339743</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2027,22 +2027,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06501690067497615</v>
+        <v>0.06500298409071253</v>
       </c>
       <c r="C8">
-        <v>381.496540528284</v>
+        <v>377.7001334705476</v>
       </c>
       <c r="D8">
-        <v>400.9785405282839</v>
+        <v>401.2691334705476</v>
       </c>
       <c r="E8">
-        <v>4.821999999999999</v>
+        <v>8.908999999999995</v>
       </c>
       <c r="F8">
-        <v>24.522</v>
+        <v>28.60899999999999</v>
       </c>
       <c r="G8">
         <v>5.04</v>
@@ -2063,28 +2063,28 @@
         <v>7.46</v>
       </c>
       <c r="M8">
-        <v>1.3560666</v>
+        <v>1.5820777</v>
       </c>
       <c r="N8">
-        <v>6.1039334</v>
+        <v>5.8779223</v>
       </c>
       <c r="O8">
-        <v>0.8911742763999999</v>
+        <v>0.8581766557999999</v>
       </c>
       <c r="P8">
-        <v>5.2127591236</v>
+        <v>5.0197456442</v>
       </c>
       <c r="Q8">
-        <v>-2.2472408764</v>
+        <v>-2.4402543558</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06615247731380441</v>
+        <v>0.0663410216029167</v>
       </c>
       <c r="T8">
-        <v>0.4700341181017184</v>
+        <v>0.4743884896747506</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.501204734339744</v>
+        <v>4.715318343719781</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2109,22 +2109,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06500298409071253</v>
+        <v>0.06539898750644892</v>
       </c>
       <c r="C9">
-        <v>377.7001334705476</v>
+        <v>365.5053703816825</v>
       </c>
       <c r="D9">
-        <v>401.2691334705476</v>
+        <v>393.1613703816824</v>
       </c>
       <c r="E9">
-        <v>8.909000000000002</v>
+        <v>12.996</v>
       </c>
       <c r="F9">
-        <v>28.609</v>
+        <v>32.696</v>
       </c>
       <c r="G9">
         <v>5.04</v>
@@ -2145,45 +2145,45 @@
         <v>7.46</v>
       </c>
       <c r="M9">
-        <v>1.5820777</v>
+        <v>2.0042648</v>
       </c>
       <c r="N9">
-        <v>5.8779223</v>
+        <v>5.455735199999999</v>
       </c>
       <c r="O9">
-        <v>0.8581766557999999</v>
+        <v>0.7965373391999999</v>
       </c>
       <c r="P9">
-        <v>5.0197456442</v>
+        <v>4.659197860799999</v>
       </c>
       <c r="Q9">
-        <v>-2.4402543558</v>
+        <v>-2.800802139200001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0663410216029167</v>
+        <v>0.06653366468092273</v>
       </c>
       <c r="T9">
-        <v>0.4743884896747506</v>
+        <v>0.4788375214993703</v>
       </c>
       <c r="U9">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0472262</v>
+        <v>0.0523502</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.71531834371978</v>
+        <v>3.722063072703766</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2191,22 +2191,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06539898750644892</v>
+        <v>0.06565151892218531</v>
       </c>
       <c r="C10">
-        <v>365.5053703816825</v>
+        <v>356.4169597659745</v>
       </c>
       <c r="D10">
-        <v>393.1613703816824</v>
+        <v>388.1599597659745</v>
       </c>
       <c r="E10">
-        <v>12.996</v>
+        <v>17.08299999999999</v>
       </c>
       <c r="F10">
-        <v>32.696</v>
+        <v>36.78299999999999</v>
       </c>
       <c r="G10">
         <v>5.04</v>
@@ -2227,45 +2227,45 @@
         <v>7.46</v>
       </c>
       <c r="M10">
-        <v>2.0042648</v>
+        <v>2.3577903</v>
       </c>
       <c r="N10">
-        <v>5.455735199999999</v>
+        <v>5.1022097</v>
       </c>
       <c r="O10">
-        <v>0.7965373391999999</v>
+        <v>0.7449226162</v>
       </c>
       <c r="P10">
-        <v>4.659197860799999</v>
+        <v>4.3572870838</v>
       </c>
       <c r="Q10">
-        <v>-2.800802139200001</v>
+        <v>-3.1027129162</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06653366468092273</v>
+        <v>0.0667305416727311</v>
       </c>
       <c r="T10">
-        <v>0.4788375214993703</v>
+        <v>0.4833843342432124</v>
       </c>
       <c r="U10">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.722063072703766</v>
+        <v>3.163979425990514</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2273,22 +2273,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06565151892218531</v>
+        <v>0.06637887433792168</v>
       </c>
       <c r="C11">
-        <v>356.4169597659745</v>
+        <v>338.6105383694634</v>
       </c>
       <c r="D11">
-        <v>388.1599597659745</v>
+        <v>374.4405383694634</v>
       </c>
       <c r="E11">
-        <v>17.08299999999999</v>
+        <v>21.17</v>
       </c>
       <c r="F11">
-        <v>36.78299999999999</v>
+        <v>40.87</v>
       </c>
       <c r="G11">
         <v>5.04</v>
@@ -2309,45 +2309,45 @@
         <v>7.46</v>
       </c>
       <c r="M11">
-        <v>2.3577903</v>
+        <v>2.938553</v>
       </c>
       <c r="N11">
-        <v>5.1022097</v>
+        <v>4.521447</v>
       </c>
       <c r="O11">
-        <v>0.7449226162</v>
+        <v>0.6601312619999999</v>
       </c>
       <c r="P11">
-        <v>4.3572870838</v>
+        <v>3.861315738</v>
       </c>
       <c r="Q11">
-        <v>-3.1027129162</v>
+        <v>-3.598684262</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0667305416727311</v>
+        <v>0.06693179370880187</v>
       </c>
       <c r="T11">
-        <v>0.4833843342432124</v>
+        <v>0.488032187270251</v>
       </c>
       <c r="U11">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.163979425990514</v>
+        <v>2.538664437905322</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2355,22 +2355,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06637887433792168</v>
+        <v>0.06687308775365806</v>
       </c>
       <c r="C12">
-        <v>338.6105383694634</v>
+        <v>325.7420280554081</v>
       </c>
       <c r="D12">
-        <v>374.4405383694634</v>
+        <v>365.659028055408</v>
       </c>
       <c r="E12">
-        <v>21.17000000000001</v>
+        <v>25.257</v>
       </c>
       <c r="F12">
-        <v>40.87</v>
+        <v>44.957</v>
       </c>
       <c r="G12">
         <v>5.04</v>
@@ -2391,45 +2391,45 @@
         <v>7.46</v>
       </c>
       <c r="M12">
-        <v>2.938553000000001</v>
+        <v>3.4077406</v>
       </c>
       <c r="N12">
-        <v>4.521446999999999</v>
+        <v>4.0522594</v>
       </c>
       <c r="O12">
-        <v>0.6601312619999998</v>
+        <v>0.5916298723999999</v>
       </c>
       <c r="P12">
-        <v>3.861315738</v>
+        <v>3.4606295276</v>
       </c>
       <c r="Q12">
-        <v>-3.598684262</v>
+        <v>-3.9993704724</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06693179370880187</v>
+        <v>0.06713756826253715</v>
       </c>
       <c r="T12">
-        <v>0.488032187270251</v>
+        <v>0.4927844864327288</v>
       </c>
       <c r="U12">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.538664437905322</v>
+        <v>2.189133762117926</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2437,22 +2437,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06687308775365806</v>
+        <v>0.06703424116939445</v>
       </c>
       <c r="C13">
-        <v>325.7420280554081</v>
+        <v>318.8799252911562</v>
       </c>
       <c r="D13">
-        <v>365.659028055408</v>
+        <v>362.8839252911562</v>
       </c>
       <c r="E13">
-        <v>25.257</v>
+        <v>29.344</v>
       </c>
       <c r="F13">
-        <v>44.957</v>
+        <v>49.044</v>
       </c>
       <c r="G13">
         <v>5.04</v>
@@ -2473,28 +2473,28 @@
         <v>7.46</v>
       </c>
       <c r="M13">
-        <v>3.4077406</v>
+        <v>3.7175352</v>
       </c>
       <c r="N13">
-        <v>4.0522594</v>
+        <v>3.7424648</v>
       </c>
       <c r="O13">
-        <v>0.5916298723999999</v>
+        <v>0.5463998608</v>
       </c>
       <c r="P13">
-        <v>3.4606295276</v>
+        <v>3.1960649392</v>
       </c>
       <c r="Q13">
-        <v>-3.9993704724</v>
+        <v>-4.2639350608</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06713756826253715</v>
+        <v>0.06734801951067551</v>
       </c>
       <c r="T13">
-        <v>0.4927844864327288</v>
+        <v>0.4976447923943537</v>
       </c>
       <c r="U13">
         <v>0.07580000000000001</v>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.189133762117926</v>
+        <v>2.006705948608099</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2519,22 +2519,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06703424116939445</v>
+        <v>0.06877187858513083</v>
       </c>
       <c r="C14">
-        <v>318.8799252911562</v>
+        <v>287.3436819121953</v>
       </c>
       <c r="D14">
-        <v>362.8839252911562</v>
+        <v>335.4346819121953</v>
       </c>
       <c r="E14">
-        <v>29.344</v>
+        <v>33.431</v>
       </c>
       <c r="F14">
-        <v>49.044</v>
+        <v>53.131</v>
       </c>
       <c r="G14">
         <v>5.04</v>
@@ -2555,45 +2555,45 @@
         <v>7.46</v>
       </c>
       <c r="M14">
-        <v>3.7175352</v>
+        <v>4.78179</v>
       </c>
       <c r="N14">
-        <v>3.7424648</v>
+        <v>2.67821</v>
       </c>
       <c r="O14">
-        <v>0.5463998608</v>
+        <v>0.39101866</v>
       </c>
       <c r="P14">
-        <v>3.1960649392</v>
+        <v>2.28719134</v>
       </c>
       <c r="Q14">
-        <v>-4.2639350608</v>
+        <v>-5.172808659999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06734801951067551</v>
+        <v>0.06756330871854119</v>
       </c>
       <c r="T14">
-        <v>0.4976447923943537</v>
+        <v>0.5026168295275103</v>
       </c>
       <c r="U14">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.006705948608099</v>
+        <v>1.560085240046091</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06877187858513083</v>
+        <v>0.07622509225830523</v>
       </c>
       <c r="C15">
-        <v>287.3436819121953</v>
+        <v>201.0854813630028</v>
       </c>
       <c r="D15">
-        <v>335.4346819121953</v>
+        <v>253.2634813630028</v>
       </c>
       <c r="E15">
-        <v>33.431</v>
+        <v>37.518</v>
       </c>
       <c r="F15">
-        <v>53.131</v>
+        <v>57.218</v>
       </c>
       <c r="G15">
         <v>5.04</v>
@@ -2637,45 +2637,45 @@
         <v>7.46</v>
       </c>
       <c r="M15">
-        <v>4.78179</v>
+        <v>8.399602400000001</v>
       </c>
       <c r="N15">
-        <v>2.67821</v>
+        <v>-0.9396024000000009</v>
       </c>
       <c r="O15">
-        <v>0.39101866</v>
+        <v>-0.1371819504000001</v>
       </c>
       <c r="P15">
-        <v>2.28719134</v>
+        <v>-0.8024204496000008</v>
       </c>
       <c r="Q15">
-        <v>-5.172808659999999</v>
+        <v>-8.2624204496</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06756330871854119</v>
+        <v>0.06783491844808369</v>
       </c>
       <c r="T15">
-        <v>0.5026168295275103</v>
+        <v>0.5088895715492768</v>
       </c>
       <c r="U15">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.146</v>
+        <v>0.1296680423825775</v>
       </c>
       <c r="W15">
-        <v>0.07686</v>
+        <v>0.1277647313782376</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y15">
-        <v>1.560085240046091</v>
+        <v>0.8881372765929967</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2683,22 +2683,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07622509225830523</v>
+        <v>0.07723509225830524</v>
       </c>
       <c r="C16">
-        <v>201.0854813630028</v>
+        <v>188.8612023604558</v>
       </c>
       <c r="D16">
-        <v>253.2634813630028</v>
+        <v>245.1262023604558</v>
       </c>
       <c r="E16">
-        <v>37.518</v>
+        <v>41.605</v>
       </c>
       <c r="F16">
-        <v>57.218</v>
+        <v>61.30500000000001</v>
       </c>
       <c r="G16">
         <v>5.04</v>
@@ -2719,37 +2719,37 @@
         <v>7.46</v>
       </c>
       <c r="M16">
-        <v>8.399602400000001</v>
+        <v>8.999574000000003</v>
       </c>
       <c r="N16">
-        <v>-0.9396024000000009</v>
+        <v>-1.539574000000003</v>
       </c>
       <c r="O16">
-        <v>-0.1371819504000001</v>
+        <v>-0.2247778040000004</v>
       </c>
       <c r="P16">
-        <v>-0.8024204496000008</v>
+        <v>-1.314796196000002</v>
       </c>
       <c r="Q16">
-        <v>-8.2624204496</v>
+        <v>-8.774796196000002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06783491844808369</v>
+        <v>0.06809415278276702</v>
       </c>
       <c r="T16">
-        <v>0.5088895715492768</v>
+        <v>0.5148765076851507</v>
       </c>
       <c r="U16">
         <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.1296680423825775</v>
+        <v>0.121023506223739</v>
       </c>
       <c r="W16">
-        <v>0.1277647313782376</v>
+        <v>0.1290337492863551</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.8881372765929967</v>
+        <v>0.8289281248201301</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2765,22 +2765,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07723509225830524</v>
+        <v>0.08697931535103988</v>
       </c>
       <c r="C17">
-        <v>188.8612023604558</v>
+        <v>126.7702170752857</v>
       </c>
       <c r="D17">
-        <v>245.1262023604558</v>
+        <v>187.1222170752857</v>
       </c>
       <c r="E17">
-        <v>41.60499999999999</v>
+        <v>45.69199999999999</v>
       </c>
       <c r="F17">
-        <v>61.30499999999999</v>
+        <v>65.392</v>
       </c>
       <c r="G17">
         <v>5.04</v>
@@ -2801,45 +2801,45 @@
         <v>7.46</v>
       </c>
       <c r="M17">
-        <v>8.999573999999999</v>
+        <v>13.1307136</v>
       </c>
       <c r="N17">
-        <v>-1.539573999999999</v>
+        <v>-5.6707136</v>
       </c>
       <c r="O17">
-        <v>-0.2247778039999999</v>
+        <v>-0.8279241855999999</v>
       </c>
       <c r="P17">
-        <v>-1.314796195999999</v>
+        <v>-4.8427894144</v>
       </c>
       <c r="Q17">
-        <v>-8.774796195999999</v>
+        <v>-12.3027894144</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.06809415278276702</v>
+        <v>0.06847172971200788</v>
       </c>
       <c r="T17">
-        <v>0.5148765076851507</v>
+        <v>0.5235965291456784</v>
       </c>
       <c r="U17">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.121023506223739</v>
+        <v>0.08294751017949244</v>
       </c>
       <c r="W17">
-        <v>0.1290337492863551</v>
+        <v>0.1841441399559579</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y17">
-        <v>0.8289281248201305</v>
+        <v>0.5681336313663867</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2847,22 +2847,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08697931535103988</v>
+        <v>0.08852931535103989</v>
       </c>
       <c r="C18">
-        <v>126.7702170752857</v>
+        <v>115.8953845513172</v>
       </c>
       <c r="D18">
-        <v>187.1222170752857</v>
+        <v>180.3343845513172</v>
       </c>
       <c r="E18">
-        <v>45.69199999999999</v>
+        <v>49.779</v>
       </c>
       <c r="F18">
-        <v>65.392</v>
+        <v>69.479</v>
       </c>
       <c r="G18">
         <v>5.04</v>
@@ -2883,37 +2883,37 @@
         <v>7.46</v>
       </c>
       <c r="M18">
-        <v>13.1307136</v>
+        <v>13.9513832</v>
       </c>
       <c r="N18">
-        <v>-5.6707136</v>
+        <v>-6.4913832</v>
       </c>
       <c r="O18">
-        <v>-0.8279241855999999</v>
+        <v>-0.9477419472</v>
       </c>
       <c r="P18">
-        <v>-4.8427894144</v>
+        <v>-5.543641252800001</v>
       </c>
       <c r="Q18">
-        <v>-12.3027894144</v>
+        <v>-13.0036412528</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.06847172971200788</v>
+        <v>0.06874488308203207</v>
       </c>
       <c r="T18">
-        <v>0.5235965291456784</v>
+        <v>0.5299049210630962</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.08294751017949244</v>
+        <v>0.07806824487481642</v>
       </c>
       <c r="W18">
-        <v>0.1841441399559579</v>
+        <v>0.1851238964291369</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.5681336313663867</v>
+        <v>0.5347140059918933</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2929,22 +2929,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08852931535103989</v>
+        <v>0.09007931535103988</v>
       </c>
       <c r="C19">
-        <v>115.8953845513172</v>
+        <v>105.4957689691077</v>
       </c>
       <c r="D19">
-        <v>180.3343845513172</v>
+        <v>174.0217689691077</v>
       </c>
       <c r="E19">
-        <v>49.779</v>
+        <v>53.866</v>
       </c>
       <c r="F19">
-        <v>69.479</v>
+        <v>73.566</v>
       </c>
       <c r="G19">
         <v>5.04</v>
@@ -2965,37 +2965,37 @@
         <v>7.46</v>
       </c>
       <c r="M19">
-        <v>13.9513832</v>
+        <v>14.7720528</v>
       </c>
       <c r="N19">
-        <v>-6.4913832</v>
+        <v>-7.312052800000001</v>
       </c>
       <c r="O19">
-        <v>-0.9477419472</v>
+        <v>-1.0675597088</v>
       </c>
       <c r="P19">
-        <v>-5.543641252800001</v>
+        <v>-6.244493091200001</v>
       </c>
       <c r="Q19">
-        <v>-13.0036412528</v>
+        <v>-13.7044930912</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.06874488308203207</v>
+        <v>0.06902469872937392</v>
       </c>
       <c r="T19">
-        <v>0.5299049210630962</v>
+        <v>0.536367176198012</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.07806824487481642</v>
+        <v>0.07373112015954884</v>
       </c>
       <c r="W19">
-        <v>0.1851238964291369</v>
+        <v>0.1859947910719626</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.5347140059918933</v>
+        <v>0.505007672325677</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3011,22 +3011,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09007931535103988</v>
+        <v>0.09831733550704706</v>
       </c>
       <c r="C20">
-        <v>105.4957689691077</v>
+        <v>74.1112142376959</v>
       </c>
       <c r="D20">
-        <v>174.0217689691077</v>
+        <v>146.7242142376959</v>
       </c>
       <c r="E20">
-        <v>53.86599999999999</v>
+        <v>57.953</v>
       </c>
       <c r="F20">
-        <v>73.56599999999999</v>
+        <v>77.65300000000001</v>
       </c>
       <c r="G20">
         <v>5.04</v>
@@ -3047,45 +3047,45 @@
         <v>7.46</v>
       </c>
       <c r="M20">
-        <v>14.7720528</v>
+        <v>18.3105774</v>
       </c>
       <c r="N20">
-        <v>-7.312052799999997</v>
+        <v>-10.8505774</v>
       </c>
       <c r="O20">
-        <v>-1.0675597088</v>
+        <v>-1.5841843004</v>
       </c>
       <c r="P20">
-        <v>-6.244493091199998</v>
+        <v>-9.266393099600002</v>
       </c>
       <c r="Q20">
-        <v>-13.7044930912</v>
+        <v>-16.7263930996</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.06902469872937392</v>
+        <v>0.06935836186925159</v>
       </c>
       <c r="T20">
-        <v>0.536367176198012</v>
+        <v>0.5440730223845633</v>
       </c>
       <c r="U20">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07373112015954886</v>
+        <v>0.05948255897162476</v>
       </c>
       <c r="W20">
-        <v>0.1859947910719626</v>
+        <v>0.2217740125944909</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.5050076723256771</v>
+        <v>0.4074147874768821</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3093,22 +3093,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09831733550704706</v>
+        <v>0.1002173355070471</v>
       </c>
       <c r="C21">
-        <v>74.1112142376959</v>
+        <v>64.90128779423711</v>
       </c>
       <c r="D21">
-        <v>146.7242142376959</v>
+        <v>141.6012877942371</v>
       </c>
       <c r="E21">
-        <v>57.953</v>
+        <v>62.04000000000001</v>
       </c>
       <c r="F21">
-        <v>77.65300000000001</v>
+        <v>81.74000000000001</v>
       </c>
       <c r="G21">
         <v>5.04</v>
@@ -3129,37 +3129,37 @@
         <v>7.46</v>
       </c>
       <c r="M21">
-        <v>18.3105774</v>
+        <v>19.274292</v>
       </c>
       <c r="N21">
-        <v>-10.8505774</v>
+        <v>-11.814292</v>
       </c>
       <c r="O21">
-        <v>-1.5841843004</v>
+        <v>-1.724886632</v>
       </c>
       <c r="P21">
-        <v>-9.266393099600002</v>
+        <v>-10.089405368</v>
       </c>
       <c r="Q21">
-        <v>-16.7263930996</v>
+        <v>-17.549405368</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.06935836186925159</v>
+        <v>0.06965284139261724</v>
       </c>
       <c r="T21">
-        <v>0.5440730223845633</v>
+        <v>0.5508739351643703</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05948255897162476</v>
+        <v>0.05650843102304354</v>
       </c>
       <c r="W21">
-        <v>0.2217740125944909</v>
+        <v>0.2224753119647664</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.4074147874768821</v>
+        <v>0.3870440481030379</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3175,22 +3175,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1002173355070471</v>
+        <v>0.1021173355070471</v>
       </c>
       <c r="C22">
-        <v>64.90128779423711</v>
+        <v>56.03702970156</v>
       </c>
       <c r="D22">
-        <v>141.6012877942371</v>
+        <v>136.82402970156</v>
       </c>
       <c r="E22">
-        <v>62.04000000000001</v>
+        <v>66.12700000000001</v>
       </c>
       <c r="F22">
-        <v>81.74000000000001</v>
+        <v>85.82700000000001</v>
       </c>
       <c r="G22">
         <v>5.04</v>
@@ -3211,37 +3211,37 @@
         <v>7.46</v>
       </c>
       <c r="M22">
-        <v>19.274292</v>
+        <v>20.2380066</v>
       </c>
       <c r="N22">
-        <v>-11.814292</v>
+        <v>-12.7780066</v>
       </c>
       <c r="O22">
-        <v>-1.724886632</v>
+        <v>-1.8655889636</v>
       </c>
       <c r="P22">
-        <v>-10.089405368</v>
+        <v>-10.9124176364</v>
       </c>
       <c r="Q22">
-        <v>-17.549405368</v>
+        <v>-18.3724176364</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.06965284139261724</v>
+        <v>0.06995477609378961</v>
       </c>
       <c r="T22">
-        <v>0.5508739351643703</v>
+        <v>0.5578470229512612</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05650843102304354</v>
+        <v>0.05381755335527956</v>
       </c>
       <c r="W22">
-        <v>0.2224753119647664</v>
+        <v>0.2231098209188251</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3870440481030379</v>
+        <v>0.3686133791457504</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3257,22 +3257,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1021173355070471</v>
+        <v>0.1040173355070471</v>
       </c>
       <c r="C23">
-        <v>56.03702970156004</v>
+        <v>47.48459592365215</v>
       </c>
       <c r="D23">
-        <v>136.8240297015601</v>
+        <v>132.3585959236522</v>
       </c>
       <c r="E23">
-        <v>66.127</v>
+        <v>70.214</v>
       </c>
       <c r="F23">
-        <v>85.827</v>
+        <v>89.914</v>
       </c>
       <c r="G23">
         <v>5.04</v>
@@ -3293,37 +3293,37 @@
         <v>7.46</v>
       </c>
       <c r="M23">
-        <v>20.2380066</v>
+        <v>21.2017212</v>
       </c>
       <c r="N23">
-        <v>-12.7780066</v>
+        <v>-13.7417212</v>
       </c>
       <c r="O23">
-        <v>-1.8655889636</v>
+        <v>-2.0062912952</v>
       </c>
       <c r="P23">
-        <v>-10.9124176364</v>
+        <v>-11.7354299048</v>
       </c>
       <c r="Q23">
-        <v>-18.3724176364</v>
+        <v>-19.1954299048</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.06995477609378961</v>
+        <v>0.07026445271037665</v>
       </c>
       <c r="T23">
-        <v>0.5578470229512612</v>
+        <v>0.5649989078608927</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05381755335527956</v>
+        <v>0.05137130093003958</v>
       </c>
       <c r="W23">
-        <v>0.2231098209188251</v>
+        <v>0.2236866472406967</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3686133791457504</v>
+        <v>0.3518582255482163</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3339,22 +3339,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1040173355070471</v>
+        <v>0.1059173355070471</v>
       </c>
       <c r="C24">
-        <v>47.48459592365215</v>
+        <v>39.21442096864334</v>
       </c>
       <c r="D24">
-        <v>132.3585959236522</v>
+        <v>128.1754209686434</v>
       </c>
       <c r="E24">
-        <v>70.214</v>
+        <v>74.301</v>
       </c>
       <c r="F24">
-        <v>89.914</v>
+        <v>94.001</v>
       </c>
       <c r="G24">
         <v>5.04</v>
@@ -3375,37 +3375,37 @@
         <v>7.46</v>
       </c>
       <c r="M24">
-        <v>21.2017212</v>
+        <v>22.1654358</v>
       </c>
       <c r="N24">
-        <v>-13.7417212</v>
+        <v>-14.7054358</v>
       </c>
       <c r="O24">
-        <v>-2.0062912952</v>
+        <v>-2.1469936268</v>
       </c>
       <c r="P24">
-        <v>-11.7354299048</v>
+        <v>-12.5584421732</v>
       </c>
       <c r="Q24">
-        <v>-19.1954299048</v>
+        <v>-20.0184421732</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07026445271037665</v>
+        <v>0.07058217287544648</v>
       </c>
       <c r="T24">
-        <v>0.5649989078608927</v>
+        <v>0.5723365560149303</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.05137130093003958</v>
+        <v>0.04913776610699438</v>
       </c>
       <c r="W24">
-        <v>0.2236866472406967</v>
+        <v>0.2242133147519707</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3518582255482163</v>
+        <v>0.3365600418287287</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3421,22 +3421,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1059173355070471</v>
+        <v>0.1078173355070471</v>
       </c>
       <c r="C25">
-        <v>39.21442096864334</v>
+        <v>31.20056248868256</v>
       </c>
       <c r="D25">
-        <v>128.1754209686434</v>
+        <v>124.2485624886826</v>
       </c>
       <c r="E25">
-        <v>74.301</v>
+        <v>78.38800000000001</v>
       </c>
       <c r="F25">
-        <v>94.001</v>
+        <v>98.08800000000001</v>
       </c>
       <c r="G25">
         <v>5.04</v>
@@ -3457,37 +3457,37 @@
         <v>7.46</v>
       </c>
       <c r="M25">
-        <v>22.1654358</v>
+        <v>23.1291504</v>
       </c>
       <c r="N25">
-        <v>-14.7054358</v>
+        <v>-15.6691504</v>
       </c>
       <c r="O25">
-        <v>-2.1469936268</v>
+        <v>-2.287695958400001</v>
       </c>
       <c r="P25">
-        <v>-12.5584421732</v>
+        <v>-13.3814544416</v>
       </c>
       <c r="Q25">
-        <v>-20.0184421732</v>
+        <v>-20.8414544416</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07058217287544648</v>
+        <v>0.07090825409749182</v>
       </c>
       <c r="T25">
-        <v>0.5723365560149303</v>
+        <v>0.5798673001730215</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04913776610699438</v>
+        <v>0.04709035918586961</v>
       </c>
       <c r="W25">
-        <v>0.2242133147519707</v>
+        <v>0.224696093303972</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3365600418287287</v>
+        <v>0.3225367067525317</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3503,22 +3503,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1078173355070471</v>
+        <v>0.1097173355070471</v>
       </c>
       <c r="C26">
-        <v>31.20056248868258</v>
+        <v>23.42016277394529</v>
       </c>
       <c r="D26">
-        <v>124.2485624886826</v>
+        <v>120.5551627739453</v>
       </c>
       <c r="E26">
-        <v>78.38799999999999</v>
+        <v>82.47499999999999</v>
       </c>
       <c r="F26">
-        <v>98.08799999999999</v>
+        <v>102.175</v>
       </c>
       <c r="G26">
         <v>5.04</v>
@@ -3539,37 +3539,37 @@
         <v>7.46</v>
       </c>
       <c r="M26">
-        <v>23.1291504</v>
+        <v>24.092865</v>
       </c>
       <c r="N26">
-        <v>-15.6691504</v>
+        <v>-16.632865</v>
       </c>
       <c r="O26">
-        <v>-2.2876959584</v>
+        <v>-2.42839829</v>
       </c>
       <c r="P26">
-        <v>-13.3814544416</v>
+        <v>-14.20446671</v>
       </c>
       <c r="Q26">
-        <v>-20.8414544416</v>
+        <v>-21.66446671</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07090825409749182</v>
+        <v>0.07124303081879171</v>
       </c>
       <c r="T26">
-        <v>0.5798673001730215</v>
+        <v>0.5875988641753285</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.04709035918586962</v>
+        <v>0.04520674481843483</v>
       </c>
       <c r="W26">
-        <v>0.224696093303972</v>
+        <v>0.2251402495718131</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3225367067525317</v>
+        <v>0.3096352384824305</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3585,22 +3585,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1097173355070471</v>
+        <v>0.1116173355070471</v>
       </c>
       <c r="C27">
-        <v>23.42016277394529</v>
+        <v>15.8530035194587</v>
       </c>
       <c r="D27">
-        <v>120.5551627739453</v>
+        <v>117.0750035194587</v>
       </c>
       <c r="E27">
-        <v>82.47499999999999</v>
+        <v>86.562</v>
       </c>
       <c r="F27">
-        <v>102.175</v>
+        <v>106.262</v>
       </c>
       <c r="G27">
         <v>5.04</v>
@@ -3621,37 +3621,37 @@
         <v>7.46</v>
       </c>
       <c r="M27">
-        <v>24.092865</v>
+        <v>25.0565796</v>
       </c>
       <c r="N27">
-        <v>-16.632865</v>
+        <v>-17.5965796</v>
       </c>
       <c r="O27">
-        <v>-2.42839829</v>
+        <v>-2.5691006216</v>
       </c>
       <c r="P27">
-        <v>-14.20446671</v>
+        <v>-15.0274789784</v>
       </c>
       <c r="Q27">
-        <v>-21.66446671</v>
+        <v>-22.4874789784</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07124303081879171</v>
+        <v>0.0715868555595862</v>
       </c>
       <c r="T27">
-        <v>0.5875988641753285</v>
+        <v>0.595539389366887</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04520674481843483</v>
+        <v>0.04346802386387964</v>
       </c>
       <c r="W27">
-        <v>0.2251402495718131</v>
+        <v>0.2255502399728972</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3096352384824305</v>
+        <v>0.2977261908484907</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1116173355070471</v>
+        <v>0.1135173355070471</v>
       </c>
       <c r="C28">
-        <v>15.8530035194587</v>
+        <v>8.481135545528758</v>
       </c>
       <c r="D28">
-        <v>117.0750035194587</v>
+        <v>113.7901355455288</v>
       </c>
       <c r="E28">
-        <v>86.562</v>
+        <v>90.649</v>
       </c>
       <c r="F28">
-        <v>106.262</v>
+        <v>110.349</v>
       </c>
       <c r="G28">
         <v>5.04</v>
@@ -3703,37 +3703,37 @@
         <v>7.46</v>
       </c>
       <c r="M28">
-        <v>25.0565796</v>
+        <v>26.0202942</v>
       </c>
       <c r="N28">
-        <v>-17.5965796</v>
+        <v>-18.5602942</v>
       </c>
       <c r="O28">
-        <v>-2.5691006216</v>
+        <v>-2.7098029532</v>
       </c>
       <c r="P28">
-        <v>-15.0274789784</v>
+        <v>-15.8504912468</v>
       </c>
       <c r="Q28">
-        <v>-22.4874789784</v>
+        <v>-23.3104912468</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0715868555595862</v>
+        <v>0.07194010015629286</v>
       </c>
       <c r="T28">
-        <v>0.595539389366887</v>
+        <v>0.6036974631938306</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04346802386387964</v>
+        <v>0.04185809705410632</v>
       </c>
       <c r="W28">
-        <v>0.2255502399728972</v>
+        <v>0.2259298607146417</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2977261908484907</v>
+        <v>0.2866992948911392</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3749,22 +3749,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1135173355070471</v>
+        <v>0.1154173355070471</v>
       </c>
       <c r="C29">
-        <v>8.481135545528758</v>
+        <v>1.288569152304461</v>
       </c>
       <c r="D29">
-        <v>113.7901355455288</v>
+        <v>110.6845691523045</v>
       </c>
       <c r="E29">
-        <v>90.649</v>
+        <v>94.736</v>
       </c>
       <c r="F29">
-        <v>110.349</v>
+        <v>114.436</v>
       </c>
       <c r="G29">
         <v>5.04</v>
@@ -3785,37 +3785,37 @@
         <v>7.46</v>
       </c>
       <c r="M29">
-        <v>26.0202942</v>
+        <v>26.9840088</v>
       </c>
       <c r="N29">
-        <v>-18.5602942</v>
+        <v>-19.5240088</v>
       </c>
       <c r="O29">
-        <v>-2.7098029532</v>
+        <v>-2.8505052848</v>
       </c>
       <c r="P29">
-        <v>-15.8504912468</v>
+        <v>-16.6735035152</v>
       </c>
       <c r="Q29">
-        <v>-23.3104912468</v>
+        <v>-24.1335035152</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07194010015629286</v>
+        <v>0.07230315710290805</v>
       </c>
       <c r="T29">
-        <v>0.6036974631938306</v>
+        <v>0.6120821501826339</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04185809705410632</v>
+        <v>0.04036316501645967</v>
       </c>
       <c r="W29">
-        <v>0.2259298607146417</v>
+        <v>0.2262823656891188</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2866992948911392</v>
+        <v>0.2764600343593129</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3831,22 +3831,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1154173355070471</v>
+        <v>0.1173173355070471</v>
       </c>
       <c r="C30">
-        <v>1.288569152304461</v>
+        <v>-5.738986167582439</v>
       </c>
       <c r="D30">
-        <v>110.6845691523045</v>
+        <v>107.7440138324176</v>
       </c>
       <c r="E30">
-        <v>94.736</v>
+        <v>98.82300000000001</v>
       </c>
       <c r="F30">
-        <v>114.436</v>
+        <v>118.523</v>
       </c>
       <c r="G30">
         <v>5.04</v>
@@ -3867,37 +3867,37 @@
         <v>7.46</v>
       </c>
       <c r="M30">
-        <v>26.9840088</v>
+        <v>27.9477234</v>
       </c>
       <c r="N30">
-        <v>-19.5240088</v>
+        <v>-20.4877234</v>
       </c>
       <c r="O30">
-        <v>-2.8505052848</v>
+        <v>-2.991207616400001</v>
       </c>
       <c r="P30">
-        <v>-16.6735035152</v>
+        <v>-17.4965157836</v>
       </c>
       <c r="Q30">
-        <v>-24.1335035152</v>
+        <v>-24.9565157836</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07230315710290805</v>
+        <v>0.0726764410057659</v>
       </c>
       <c r="T30">
-        <v>0.6120821501826339</v>
+        <v>0.6207030255373188</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04036316501645967</v>
+        <v>0.03897133174003002</v>
       </c>
       <c r="W30">
-        <v>0.2262823656891188</v>
+        <v>0.226610559975701</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2764600343593129</v>
+        <v>0.2669269297262331</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3913,22 +3913,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1173173355070471</v>
+        <v>0.1192173355070471</v>
       </c>
       <c r="C31">
-        <v>-5.738986167582411</v>
+        <v>-12.61434159982147</v>
       </c>
       <c r="D31">
-        <v>107.7440138324176</v>
+        <v>104.9556584001785</v>
       </c>
       <c r="E31">
-        <v>98.82299999999998</v>
+        <v>102.91</v>
       </c>
       <c r="F31">
-        <v>118.523</v>
+        <v>122.61</v>
       </c>
       <c r="G31">
         <v>5.04</v>
@@ -3949,37 +3949,37 @@
         <v>7.46</v>
       </c>
       <c r="M31">
-        <v>27.9477234</v>
+        <v>28.911438</v>
       </c>
       <c r="N31">
-        <v>-20.4877234</v>
+        <v>-21.451438</v>
       </c>
       <c r="O31">
-        <v>-2.991207616399999</v>
+        <v>-3.131909947999999</v>
       </c>
       <c r="P31">
-        <v>-17.4965157836</v>
+        <v>-18.319528052</v>
       </c>
       <c r="Q31">
-        <v>-24.9565157836</v>
+        <v>-25.779528052</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0726764410057659</v>
+        <v>0.07306039016299112</v>
       </c>
       <c r="T31">
-        <v>0.6207030255373188</v>
+        <v>0.6295702116164233</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03897133174003003</v>
+        <v>0.0376722873486957</v>
       </c>
       <c r="W31">
-        <v>0.226610559975701</v>
+        <v>0.2269168746431776</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2669269297262331</v>
+        <v>0.2580293654020254</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3995,22 +3995,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1192173355070471</v>
+        <v>0.1211173355070471</v>
       </c>
       <c r="C32">
-        <v>-12.61434159982147</v>
+        <v>-19.34901559967614</v>
       </c>
       <c r="D32">
-        <v>104.9556584001785</v>
+        <v>102.3079844003238</v>
       </c>
       <c r="E32">
-        <v>102.91</v>
+        <v>106.997</v>
       </c>
       <c r="F32">
-        <v>122.61</v>
+        <v>126.697</v>
       </c>
       <c r="G32">
         <v>5.04</v>
@@ -4031,37 +4031,37 @@
         <v>7.46</v>
       </c>
       <c r="M32">
-        <v>28.911438</v>
+        <v>29.8751526</v>
       </c>
       <c r="N32">
-        <v>-21.451438</v>
+        <v>-22.4151526</v>
       </c>
       <c r="O32">
-        <v>-3.131909947999999</v>
+        <v>-3.2726122796</v>
       </c>
       <c r="P32">
-        <v>-18.319528052</v>
+        <v>-19.1425403204</v>
       </c>
       <c r="Q32">
-        <v>-25.779528052</v>
+        <v>-26.6025403204</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07306039016299112</v>
+        <v>0.07345546828129534</v>
       </c>
       <c r="T32">
-        <v>0.6295702116164233</v>
+        <v>0.6386944175818787</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0376722873486957</v>
+        <v>0.03645705227293131</v>
       </c>
       <c r="W32">
-        <v>0.2269168746431776</v>
+        <v>0.2272034270740428</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2580293654020254</v>
+        <v>0.249705837485831</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4077,22 +4077,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1211173355070471</v>
+        <v>0.123017335507047</v>
       </c>
       <c r="C33">
-        <v>-19.34901559967614</v>
+        <v>-25.95339293579099</v>
       </c>
       <c r="D33">
-        <v>102.3079844003238</v>
+        <v>99.790607064209</v>
       </c>
       <c r="E33">
-        <v>106.997</v>
+        <v>111.084</v>
       </c>
       <c r="F33">
-        <v>126.697</v>
+        <v>130.784</v>
       </c>
       <c r="G33">
         <v>5.04</v>
@@ -4113,37 +4113,37 @@
         <v>7.46</v>
       </c>
       <c r="M33">
-        <v>29.8751526</v>
+        <v>30.8388672</v>
       </c>
       <c r="N33">
-        <v>-22.4151526</v>
+        <v>-23.3788672</v>
       </c>
       <c r="O33">
-        <v>-3.2726122796</v>
+        <v>-3.4133146112</v>
       </c>
       <c r="P33">
-        <v>-19.1425403204</v>
+        <v>-19.9655525888</v>
       </c>
       <c r="Q33">
-        <v>-26.6025403204</v>
+        <v>-27.4255525888</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07345546828129534</v>
+        <v>0.07386216634425558</v>
       </c>
       <c r="T33">
-        <v>0.6386944175818787</v>
+        <v>0.6480869825463181</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03645705227293131</v>
+        <v>0.03531776938940221</v>
       </c>
       <c r="W33">
-        <v>0.2272034270740428</v>
+        <v>0.227472069977979</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.249705837485831</v>
+        <v>0.2419025300643988</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4159,22 +4159,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.123017335507047</v>
+        <v>0.1249173355070471</v>
       </c>
       <c r="C34">
-        <v>-25.95339293579099</v>
+        <v>-32.43686081741103</v>
       </c>
       <c r="D34">
-        <v>99.790607064209</v>
+        <v>97.39413918258897</v>
       </c>
       <c r="E34">
-        <v>111.084</v>
+        <v>115.171</v>
       </c>
       <c r="F34">
-        <v>130.784</v>
+        <v>134.871</v>
       </c>
       <c r="G34">
         <v>5.04</v>
@@ -4195,37 +4195,37 @@
         <v>7.46</v>
       </c>
       <c r="M34">
-        <v>30.8388672</v>
+        <v>31.8025818</v>
       </c>
       <c r="N34">
-        <v>-23.3788672</v>
+        <v>-24.3425818</v>
       </c>
       <c r="O34">
-        <v>-3.4133146112</v>
+        <v>-3.5540169428</v>
       </c>
       <c r="P34">
-        <v>-19.9655525888</v>
+        <v>-20.7885648572</v>
       </c>
       <c r="Q34">
-        <v>-27.4255525888</v>
+        <v>-28.2485648572</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07386216634425558</v>
+        <v>0.07428100464790119</v>
       </c>
       <c r="T34">
-        <v>0.6480869825463181</v>
+        <v>0.6577599225843229</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03531776938940221</v>
+        <v>0.03424753395335972</v>
       </c>
       <c r="W34">
-        <v>0.227472069977979</v>
+        <v>0.2277244314937978</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2419025300643988</v>
+        <v>0.2345721503654775</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4241,22 +4241,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1249173355070471</v>
+        <v>0.1268173355070471</v>
       </c>
       <c r="C35">
-        <v>-32.43686081741103</v>
+        <v>-38.80792586705496</v>
       </c>
       <c r="D35">
-        <v>97.39413918258897</v>
+        <v>95.11007413294503</v>
       </c>
       <c r="E35">
-        <v>115.171</v>
+        <v>119.258</v>
       </c>
       <c r="F35">
-        <v>134.871</v>
+        <v>138.958</v>
       </c>
       <c r="G35">
         <v>5.04</v>
@@ -4277,37 +4277,37 @@
         <v>7.46</v>
       </c>
       <c r="M35">
-        <v>31.8025818</v>
+        <v>32.7662964</v>
       </c>
       <c r="N35">
-        <v>-24.3425818</v>
+        <v>-25.3062964</v>
       </c>
       <c r="O35">
-        <v>-3.5540169428</v>
+        <v>-3.6947192744</v>
       </c>
       <c r="P35">
-        <v>-20.7885648572</v>
+        <v>-21.6115771256</v>
       </c>
       <c r="Q35">
-        <v>-28.2485648572</v>
+        <v>-29.0715771256</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07428100464790119</v>
+        <v>0.07471253502135423</v>
       </c>
       <c r="T35">
-        <v>0.6577599225843229</v>
+        <v>0.6677259820174187</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03424753395335972</v>
+        <v>0.03324025354296679</v>
       </c>
       <c r="W35">
-        <v>0.2277244314937978</v>
+        <v>0.2279619482145684</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2345721503654775</v>
+        <v>0.2276729694723753</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4323,22 +4323,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1268173355070471</v>
+        <v>0.1287173355070471</v>
       </c>
       <c r="C36">
-        <v>-38.80792586705496</v>
+        <v>-45.0743150110445</v>
       </c>
       <c r="D36">
-        <v>95.11007413294503</v>
+        <v>92.93068498895551</v>
       </c>
       <c r="E36">
-        <v>119.258</v>
+        <v>123.345</v>
       </c>
       <c r="F36">
-        <v>138.958</v>
+        <v>143.045</v>
       </c>
       <c r="G36">
         <v>5.04</v>
@@ -4359,37 +4359,37 @@
         <v>7.46</v>
       </c>
       <c r="M36">
-        <v>32.7662964</v>
+        <v>33.730011</v>
       </c>
       <c r="N36">
-        <v>-25.3062964</v>
+        <v>-26.270011</v>
       </c>
       <c r="O36">
-        <v>-3.6947192744</v>
+        <v>-3.835421606</v>
       </c>
       <c r="P36">
-        <v>-21.6115771256</v>
+        <v>-22.434589394</v>
       </c>
       <c r="Q36">
-        <v>-29.0715771256</v>
+        <v>-29.894589394</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07471253502135423</v>
+        <v>0.07515734325245199</v>
       </c>
       <c r="T36">
-        <v>0.6677259820174187</v>
+        <v>0.6779986894330713</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03324025354296679</v>
+        <v>0.03229053201316773</v>
       </c>
       <c r="W36">
-        <v>0.2279619482145684</v>
+        <v>0.228185892551295</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2276729694723753</v>
+        <v>0.2211680274874502</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4405,22 +4405,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1287173355070471</v>
+        <v>0.1306173355070471</v>
       </c>
       <c r="C37">
-        <v>-45.0743150110445</v>
+        <v>-51.24306280969289</v>
       </c>
       <c r="D37">
-        <v>92.93068498895551</v>
+        <v>90.84893719030711</v>
       </c>
       <c r="E37">
-        <v>123.345</v>
+        <v>127.432</v>
       </c>
       <c r="F37">
-        <v>143.045</v>
+        <v>147.132</v>
       </c>
       <c r="G37">
         <v>5.04</v>
@@ -4441,37 +4441,37 @@
         <v>7.46</v>
       </c>
       <c r="M37">
-        <v>33.730011</v>
+        <v>34.6937256</v>
       </c>
       <c r="N37">
-        <v>-26.270011</v>
+        <v>-27.2337256</v>
       </c>
       <c r="O37">
-        <v>-3.835421606</v>
+        <v>-3.9761239376</v>
       </c>
       <c r="P37">
-        <v>-22.434589394</v>
+        <v>-23.2576016624</v>
       </c>
       <c r="Q37">
-        <v>-29.894589394</v>
+        <v>-30.7176016624</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07515734325245199</v>
+        <v>0.07561605174077154</v>
       </c>
       <c r="T37">
-        <v>0.6779986894330713</v>
+        <v>0.6885924189554631</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03229053201316773</v>
+        <v>0.03139357279057975</v>
       </c>
       <c r="W37">
-        <v>0.228185892551295</v>
+        <v>0.2283973955359813</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2211680274874502</v>
+        <v>0.2150244711683544</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4487,22 +4487,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1306173355070471</v>
+        <v>0.1325173355070471</v>
       </c>
       <c r="C38">
-        <v>-51.24306280969286</v>
+        <v>-57.3205873069262</v>
       </c>
       <c r="D38">
-        <v>90.84893719030711</v>
+        <v>88.85841269307379</v>
       </c>
       <c r="E38">
-        <v>127.432</v>
+        <v>131.519</v>
       </c>
       <c r="F38">
-        <v>147.132</v>
+        <v>151.219</v>
       </c>
       <c r="G38">
         <v>5.04</v>
@@ -4523,37 +4523,37 @@
         <v>7.46</v>
       </c>
       <c r="M38">
-        <v>34.69372559999999</v>
+        <v>35.6574402</v>
       </c>
       <c r="N38">
-        <v>-27.23372559999999</v>
+        <v>-28.1974402</v>
       </c>
       <c r="O38">
-        <v>-3.976123937599999</v>
+        <v>-4.1168262692</v>
       </c>
       <c r="P38">
-        <v>-23.25760166239999</v>
+        <v>-24.0806139308</v>
       </c>
       <c r="Q38">
-        <v>-30.71760166239999</v>
+        <v>-31.5406139308</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07561605174077154</v>
+        <v>0.07608932240332347</v>
       </c>
       <c r="T38">
-        <v>0.6885924189554631</v>
+        <v>0.6995224573515815</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03139357279057975</v>
+        <v>0.0305450978502938</v>
       </c>
       <c r="W38">
-        <v>0.2283973955359813</v>
+        <v>0.2285974659269007</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2150244711683545</v>
+        <v>0.2092129989746151</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4569,22 +4569,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1325173355070471</v>
+        <v>0.134417335507047</v>
       </c>
       <c r="C39">
-        <v>-57.3205873069262</v>
+        <v>-63.31275612238234</v>
       </c>
       <c r="D39">
-        <v>88.85841269307379</v>
+        <v>86.95324387761767</v>
       </c>
       <c r="E39">
-        <v>131.519</v>
+        <v>135.606</v>
       </c>
       <c r="F39">
-        <v>151.219</v>
+        <v>155.306</v>
       </c>
       <c r="G39">
         <v>5.04</v>
@@ -4605,37 +4605,37 @@
         <v>7.46</v>
       </c>
       <c r="M39">
-        <v>35.6574402</v>
+        <v>36.62115480000001</v>
       </c>
       <c r="N39">
-        <v>-28.1974402</v>
+        <v>-29.16115480000001</v>
       </c>
       <c r="O39">
-        <v>-4.1168262692</v>
+        <v>-4.257528600800001</v>
       </c>
       <c r="P39">
-        <v>-24.0806139308</v>
+        <v>-24.9036261992</v>
       </c>
       <c r="Q39">
-        <v>-31.5406139308</v>
+        <v>-32.36362619920001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07608932240332347</v>
+        <v>0.0765778598614416</v>
       </c>
       <c r="T39">
-        <v>0.6995224573515815</v>
+        <v>0.7108050776314456</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0305450978502938</v>
+        <v>0.02974127948581238</v>
       </c>
       <c r="W39">
-        <v>0.2285974659269007</v>
+        <v>0.2287870062972454</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2092129989746151</v>
+        <v>0.203707393738441</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4651,22 +4651,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.134417335507047</v>
+        <v>0.1363173355070471</v>
       </c>
       <c r="C40">
-        <v>-63.31275612238234</v>
+        <v>-69.22494421969012</v>
       </c>
       <c r="D40">
-        <v>86.95324387761767</v>
+        <v>85.12805578030988</v>
       </c>
       <c r="E40">
-        <v>135.606</v>
+        <v>139.693</v>
       </c>
       <c r="F40">
-        <v>155.306</v>
+        <v>159.393</v>
       </c>
       <c r="G40">
         <v>5.04</v>
@@ -4687,37 +4687,37 @@
         <v>7.46</v>
       </c>
       <c r="M40">
-        <v>36.62115480000001</v>
+        <v>37.5848694</v>
       </c>
       <c r="N40">
-        <v>-29.16115480000001</v>
+        <v>-30.1248694</v>
       </c>
       <c r="O40">
-        <v>-4.257528600800001</v>
+        <v>-4.3982309324</v>
       </c>
       <c r="P40">
-        <v>-24.9036261992</v>
+        <v>-25.7266384676</v>
       </c>
       <c r="Q40">
-        <v>-32.36362619920001</v>
+        <v>-33.1866384676</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0765778598614416</v>
+        <v>0.07708241494113736</v>
       </c>
       <c r="T40">
-        <v>0.7108050776314456</v>
+        <v>0.722457619887699</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02974127948581238</v>
+        <v>0.02897868257591976</v>
       </c>
       <c r="W40">
-        <v>0.2287870062972454</v>
+        <v>0.2289668266485981</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.203707393738441</v>
+        <v>0.1984841272323272</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1363173355070471</v>
+        <v>0.1382173355070471</v>
       </c>
       <c r="C41">
-        <v>-69.22494421969012</v>
+        <v>-75.06208454883063</v>
       </c>
       <c r="D41">
-        <v>85.12805578030988</v>
+        <v>83.37791545116939</v>
       </c>
       <c r="E41">
-        <v>139.693</v>
+        <v>143.78</v>
       </c>
       <c r="F41">
-        <v>159.393</v>
+        <v>163.48</v>
       </c>
       <c r="G41">
         <v>5.04</v>
@@ -4769,37 +4769,37 @@
         <v>7.46</v>
       </c>
       <c r="M41">
-        <v>37.5848694</v>
+        <v>38.54858400000001</v>
       </c>
       <c r="N41">
-        <v>-30.1248694</v>
+        <v>-31.088584</v>
       </c>
       <c r="O41">
-        <v>-4.3982309324</v>
+        <v>-4.538933264000001</v>
       </c>
       <c r="P41">
-        <v>-25.7266384676</v>
+        <v>-26.549650736</v>
       </c>
       <c r="Q41">
-        <v>-33.1866384676</v>
+        <v>-34.009650736</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07708241494113736</v>
+        <v>0.07760378852348965</v>
       </c>
       <c r="T41">
-        <v>0.722457619887699</v>
+        <v>0.7344985802191606</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02897868257591976</v>
+        <v>0.02825421551152177</v>
       </c>
       <c r="W41">
-        <v>0.2289668266485981</v>
+        <v>0.2291376559823832</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1984841272323272</v>
+        <v>0.193522024051519</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4815,22 +4815,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1382173355070471</v>
+        <v>0.1401173355070471</v>
       </c>
       <c r="C42">
-        <v>-75.06208454883063</v>
+        <v>-80.82871256742941</v>
       </c>
       <c r="D42">
-        <v>83.37791545116939</v>
+        <v>81.6982874325706</v>
       </c>
       <c r="E42">
-        <v>143.78</v>
+        <v>147.867</v>
       </c>
       <c r="F42">
-        <v>163.48</v>
+        <v>167.567</v>
       </c>
       <c r="G42">
         <v>5.04</v>
@@ -4851,37 +4851,37 @@
         <v>7.46</v>
       </c>
       <c r="M42">
-        <v>38.54858400000001</v>
+        <v>39.5122986</v>
       </c>
       <c r="N42">
-        <v>-31.088584</v>
+        <v>-32.0522986</v>
       </c>
       <c r="O42">
-        <v>-4.538933264000001</v>
+        <v>-4.6796355956</v>
       </c>
       <c r="P42">
-        <v>-26.549650736</v>
+        <v>-27.3726630044</v>
       </c>
       <c r="Q42">
-        <v>-34.009650736</v>
+        <v>-34.8326630044</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07760378852348965</v>
+        <v>0.07814283578659964</v>
       </c>
       <c r="T42">
-        <v>0.7344985802191606</v>
+        <v>0.7469477086974514</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02825421551152177</v>
+        <v>0.02756508830392368</v>
       </c>
       <c r="W42">
-        <v>0.2291376559823832</v>
+        <v>0.2293001521779348</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.193522024051519</v>
+        <v>0.1888019746844087</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4897,22 +4897,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1401173355070471</v>
+        <v>0.1420173355070471</v>
       </c>
       <c r="C43">
-        <v>-80.82871256742941</v>
+        <v>-86.52900548708752</v>
       </c>
       <c r="D43">
-        <v>81.6982874325706</v>
+        <v>80.0849945129125</v>
       </c>
       <c r="E43">
-        <v>147.867</v>
+        <v>151.954</v>
       </c>
       <c r="F43">
-        <v>167.567</v>
+        <v>171.654</v>
       </c>
       <c r="G43">
         <v>5.04</v>
@@ -4933,37 +4933,37 @@
         <v>7.46</v>
       </c>
       <c r="M43">
-        <v>39.5122986</v>
+        <v>40.4760132</v>
       </c>
       <c r="N43">
-        <v>-32.0522986</v>
+        <v>-33.0160132</v>
       </c>
       <c r="O43">
-        <v>-4.6796355956</v>
+        <v>-4.8203379272</v>
       </c>
       <c r="P43">
-        <v>-27.3726630044</v>
+        <v>-28.1956752728</v>
       </c>
       <c r="Q43">
-        <v>-34.8326630044</v>
+        <v>-35.6556752728</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07814283578659964</v>
+        <v>0.07870047088636861</v>
       </c>
       <c r="T43">
-        <v>0.7469477086974514</v>
+        <v>0.7598261174680973</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02756508830392368</v>
+        <v>0.02690877667763978</v>
       </c>
       <c r="W43">
-        <v>0.2293001521779348</v>
+        <v>0.2294549104594125</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1888019746844087</v>
+        <v>0.1843066895728752</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4979,22 +4979,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.142017335507047</v>
+        <v>0.1439173355070471</v>
       </c>
       <c r="C44">
-        <v>-86.52900548708743</v>
+        <v>-92.16681695978185</v>
       </c>
       <c r="D44">
-        <v>80.08499451291256</v>
+        <v>78.53418304021812</v>
       </c>
       <c r="E44">
-        <v>151.954</v>
+        <v>156.041</v>
       </c>
       <c r="F44">
-        <v>171.654</v>
+        <v>175.741</v>
       </c>
       <c r="G44">
         <v>5.04</v>
@@ -5015,37 +5015,37 @@
         <v>7.46</v>
       </c>
       <c r="M44">
-        <v>40.4760132</v>
+        <v>41.4397278</v>
       </c>
       <c r="N44">
-        <v>-33.0160132</v>
+        <v>-33.9797278</v>
       </c>
       <c r="O44">
-        <v>-4.8203379272</v>
+        <v>-4.9610402588</v>
       </c>
       <c r="P44">
-        <v>-28.1956752728</v>
+        <v>-29.0186875412</v>
       </c>
       <c r="Q44">
-        <v>-35.6556752728</v>
+        <v>-36.4786875412</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0787004708863686</v>
+        <v>0.0792776721299891</v>
       </c>
       <c r="T44">
-        <v>0.759826117468097</v>
+        <v>0.7731564002306952</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02690877667763978</v>
+        <v>0.02628299117350862</v>
       </c>
       <c r="W44">
-        <v>0.2294549104594125</v>
+        <v>0.2296024706812867</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1843066895728752</v>
+        <v>0.1800204874897852</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5061,22 +5061,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1439173355070471</v>
+        <v>0.1458173355070471</v>
       </c>
       <c r="C45">
-        <v>-92.16681695978185</v>
+        <v>-97.74570781070243</v>
       </c>
       <c r="D45">
-        <v>78.53418304021812</v>
+        <v>77.04229218929757</v>
       </c>
       <c r="E45">
-        <v>156.041</v>
+        <v>160.128</v>
       </c>
       <c r="F45">
-        <v>175.741</v>
+        <v>179.828</v>
       </c>
       <c r="G45">
         <v>5.04</v>
@@ -5097,37 +5097,37 @@
         <v>7.46</v>
       </c>
       <c r="M45">
-        <v>41.4397278</v>
+        <v>42.4034424</v>
       </c>
       <c r="N45">
-        <v>-33.9797278</v>
+        <v>-34.9434424</v>
       </c>
       <c r="O45">
-        <v>-4.9610402588</v>
+        <v>-5.1017425904</v>
       </c>
       <c r="P45">
-        <v>-29.0186875412</v>
+        <v>-29.8416998096</v>
       </c>
       <c r="Q45">
-        <v>-36.4786875412</v>
+        <v>-37.3016998096</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0792776721299891</v>
+        <v>0.07987548770373891</v>
       </c>
       <c r="T45">
-        <v>0.7731564002306952</v>
+        <v>0.7869627645205292</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02628299117350862</v>
+        <v>0.02568565046501979</v>
       </c>
       <c r="W45">
-        <v>0.2296024706812867</v>
+        <v>0.2297433236203483</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1800204874897852</v>
+        <v>0.1759291127741082</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5143,22 +5143,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1458173355070471</v>
+        <v>0.147717335507047</v>
       </c>
       <c r="C46">
-        <v>-97.74570781070243</v>
+        <v>-103.2689733334558</v>
       </c>
       <c r="D46">
-        <v>77.04229218929757</v>
+        <v>75.60602666654414</v>
       </c>
       <c r="E46">
-        <v>160.128</v>
+        <v>164.215</v>
       </c>
       <c r="F46">
-        <v>179.828</v>
+        <v>183.915</v>
       </c>
       <c r="G46">
         <v>5.04</v>
@@ -5179,37 +5179,37 @@
         <v>7.46</v>
       </c>
       <c r="M46">
-        <v>42.4034424</v>
+        <v>43.367157</v>
       </c>
       <c r="N46">
-        <v>-34.9434424</v>
+        <v>-35.907157</v>
       </c>
       <c r="O46">
-        <v>-5.1017425904</v>
+        <v>-5.242444922</v>
       </c>
       <c r="P46">
-        <v>-29.8416998096</v>
+        <v>-30.664712078</v>
       </c>
       <c r="Q46">
-        <v>-37.3016998096</v>
+        <v>-38.12471207799999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.07987548770373891</v>
+        <v>0.08049504202562507</v>
       </c>
       <c r="T46">
-        <v>0.7869627645205292</v>
+        <v>0.8012711784209025</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02568565046501979</v>
+        <v>0.0251148582324638</v>
       </c>
       <c r="W46">
-        <v>0.2297433236203483</v>
+        <v>0.229877916428785</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1759291127741082</v>
+        <v>0.1720195769346836</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5225,22 +5225,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.147717335507047</v>
+        <v>0.1496173355070471</v>
       </c>
       <c r="C47">
-        <v>-103.2689733334558</v>
+        <v>-108.7396675880313</v>
       </c>
       <c r="D47">
-        <v>75.60602666654414</v>
+        <v>74.22233241196867</v>
       </c>
       <c r="E47">
-        <v>164.215</v>
+        <v>168.302</v>
       </c>
       <c r="F47">
-        <v>183.915</v>
+        <v>188.002</v>
       </c>
       <c r="G47">
         <v>5.04</v>
@@ -5261,37 +5261,37 @@
         <v>7.46</v>
       </c>
       <c r="M47">
-        <v>43.367157</v>
+        <v>44.3308716</v>
       </c>
       <c r="N47">
-        <v>-35.907157</v>
+        <v>-36.8708716</v>
       </c>
       <c r="O47">
-        <v>-5.242444922</v>
+        <v>-5.3831472536</v>
       </c>
       <c r="P47">
-        <v>-30.664712078</v>
+        <v>-31.4877243464</v>
       </c>
       <c r="Q47">
-        <v>-38.12471207799999</v>
+        <v>-38.9477243464</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08049504202562507</v>
+        <v>0.08113754280387739</v>
       </c>
       <c r="T47">
-        <v>0.8012711784209025</v>
+        <v>0.8161095335768451</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0251148582324638</v>
+        <v>0.02456888305349719</v>
       </c>
       <c r="W47">
-        <v>0.229877916428785</v>
+        <v>0.2300066573759854</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1720195769346836</v>
+        <v>0.1682800209143643</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5307,22 +5307,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1496173355070471</v>
+        <v>0.1515173355070471</v>
       </c>
       <c r="C48">
-        <v>-108.7396675880313</v>
+        <v>-114.1606250786014</v>
       </c>
       <c r="D48">
-        <v>74.22233241196867</v>
+        <v>72.88837492139855</v>
       </c>
       <c r="E48">
-        <v>168.302</v>
+        <v>172.389</v>
       </c>
       <c r="F48">
-        <v>188.002</v>
+        <v>192.089</v>
       </c>
       <c r="G48">
         <v>5.04</v>
@@ -5343,37 +5343,37 @@
         <v>7.46</v>
       </c>
       <c r="M48">
-        <v>44.3308716</v>
+        <v>45.2945862</v>
       </c>
       <c r="N48">
-        <v>-36.8708716</v>
+        <v>-37.8345862</v>
       </c>
       <c r="O48">
-        <v>-5.3831472536</v>
+        <v>-5.5238495852</v>
       </c>
       <c r="P48">
-        <v>-31.4877243464</v>
+        <v>-32.31073661480001</v>
       </c>
       <c r="Q48">
-        <v>-38.9477243464</v>
+        <v>-39.77073661480001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08113754280387739</v>
+        <v>0.08180428889451659</v>
       </c>
       <c r="T48">
-        <v>0.8161095335768451</v>
+        <v>0.8315078266632007</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02456888305349719</v>
+        <v>0.02404614086086959</v>
       </c>
       <c r="W48">
-        <v>0.2300066573759854</v>
+        <v>0.230129919985007</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1682800209143643</v>
+        <v>0.164699594937463</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5389,22 +5389,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1515173355070471</v>
+        <v>0.1534173355070471</v>
       </c>
       <c r="C49">
-        <v>-114.1606250786014</v>
+        <v>-119.5344801349747</v>
       </c>
       <c r="D49">
-        <v>72.88837492139855</v>
+        <v>71.60151986502534</v>
       </c>
       <c r="E49">
-        <v>172.389</v>
+        <v>176.476</v>
       </c>
       <c r="F49">
-        <v>192.089</v>
+        <v>196.176</v>
       </c>
       <c r="G49">
         <v>5.04</v>
@@ -5425,37 +5425,37 @@
         <v>7.46</v>
       </c>
       <c r="M49">
-        <v>45.2945862</v>
+        <v>46.25830080000001</v>
       </c>
       <c r="N49">
-        <v>-37.8345862</v>
+        <v>-38.79830080000001</v>
       </c>
       <c r="O49">
-        <v>-5.5238495852</v>
+        <v>-5.664551916800001</v>
       </c>
       <c r="P49">
-        <v>-32.31073661480001</v>
+        <v>-33.13374888320001</v>
       </c>
       <c r="Q49">
-        <v>-39.77073661480001</v>
+        <v>-40.59374888320001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08180428889451659</v>
+        <v>0.08249667906556499</v>
       </c>
       <c r="T49">
-        <v>0.8315078266632007</v>
+        <v>0.8474983617913391</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02404614086086959</v>
+        <v>0.0235451795929348</v>
       </c>
       <c r="W49">
-        <v>0.230129919985007</v>
+        <v>0.230248046651986</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.164699594937463</v>
+        <v>0.1612683533762658</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5471,22 +5471,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1534173355070471</v>
+        <v>0.155317335507047</v>
       </c>
       <c r="C50">
-        <v>-119.5344801349746</v>
+        <v>-124.8636842765718</v>
       </c>
       <c r="D50">
-        <v>71.60151986502534</v>
+        <v>70.35931572342813</v>
       </c>
       <c r="E50">
-        <v>176.476</v>
+        <v>180.563</v>
       </c>
       <c r="F50">
-        <v>196.176</v>
+        <v>200.263</v>
       </c>
       <c r="G50">
         <v>5.04</v>
@@ -5507,37 +5507,37 @@
         <v>7.46</v>
       </c>
       <c r="M50">
-        <v>46.2583008</v>
+        <v>47.2220154</v>
       </c>
       <c r="N50">
-        <v>-38.7983008</v>
+        <v>-39.7620154</v>
       </c>
       <c r="O50">
-        <v>-5.6645519168</v>
+        <v>-5.805254248399999</v>
       </c>
       <c r="P50">
-        <v>-33.1337488832</v>
+        <v>-33.9567611516</v>
       </c>
       <c r="Q50">
-        <v>-40.5937488832</v>
+        <v>-41.4167611516</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08249667906556499</v>
+        <v>0.08321622179234076</v>
       </c>
       <c r="T50">
-        <v>0.8474983617913391</v>
+        <v>0.8641159767284241</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02354517959293481</v>
+        <v>0.02306466572369124</v>
       </c>
       <c r="W50">
-        <v>0.230248046651986</v>
+        <v>0.2303613518223536</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1612683533762659</v>
+        <v>0.1579771624910359</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5553,22 +5553,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.155317335507047</v>
+        <v>0.1572173355070471</v>
       </c>
       <c r="C51">
-        <v>-124.8636842765718</v>
+        <v>-130.1505217997557</v>
       </c>
       <c r="D51">
-        <v>70.35931572342813</v>
+        <v>69.15947820024427</v>
       </c>
       <c r="E51">
-        <v>180.563</v>
+        <v>184.65</v>
       </c>
       <c r="F51">
-        <v>200.263</v>
+        <v>204.35</v>
       </c>
       <c r="G51">
         <v>5.04</v>
@@ -5589,37 +5589,37 @@
         <v>7.46</v>
       </c>
       <c r="M51">
-        <v>47.2220154</v>
+        <v>48.18573</v>
       </c>
       <c r="N51">
-        <v>-39.7620154</v>
+        <v>-40.72573</v>
       </c>
       <c r="O51">
-        <v>-5.805254248399999</v>
+        <v>-5.94595658</v>
       </c>
       <c r="P51">
-        <v>-33.9567611516</v>
+        <v>-34.77977342</v>
       </c>
       <c r="Q51">
-        <v>-41.4167611516</v>
+        <v>-42.23977342</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08321622179234076</v>
+        <v>0.08396454622818758</v>
       </c>
       <c r="T51">
-        <v>0.8641159767284241</v>
+        <v>0.8813982962629927</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02306466572369124</v>
+        <v>0.02260337240921742</v>
       </c>
       <c r="W51">
-        <v>0.2303613518223536</v>
+        <v>0.2304701247859066</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1579771624910359</v>
+        <v>0.1548176192412152</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5635,22 +5635,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1572173355070471</v>
+        <v>0.1591173355070471</v>
       </c>
       <c r="C52">
-        <v>-130.1505217997557</v>
+        <v>-135.3971237970361</v>
       </c>
       <c r="D52">
-        <v>69.15947820024427</v>
+        <v>67.9998762029639</v>
       </c>
       <c r="E52">
-        <v>184.65</v>
+        <v>188.737</v>
       </c>
       <c r="F52">
-        <v>204.35</v>
+        <v>208.437</v>
       </c>
       <c r="G52">
         <v>5.04</v>
@@ -5671,37 +5671,37 @@
         <v>7.46</v>
       </c>
       <c r="M52">
-        <v>48.18573</v>
+        <v>49.1494446</v>
       </c>
       <c r="N52">
-        <v>-40.72573</v>
+        <v>-41.6894446</v>
       </c>
       <c r="O52">
-        <v>-5.94595658</v>
+        <v>-6.0866589116</v>
       </c>
       <c r="P52">
-        <v>-34.77977342</v>
+        <v>-35.6027856884</v>
       </c>
       <c r="Q52">
-        <v>-42.23977342</v>
+        <v>-43.06278568840001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08396454622818758</v>
+        <v>0.08474341451855875</v>
       </c>
       <c r="T52">
-        <v>0.8813982962629927</v>
+        <v>0.8993860165948904</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02260337240921742</v>
+        <v>0.02216016902864452</v>
       </c>
       <c r="W52">
-        <v>0.2304701247859066</v>
+        <v>0.2305746321430456</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1548176192412152</v>
+        <v>0.1517819796482502</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5717,22 +5717,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1591173355070471</v>
+        <v>0.1610173355070471</v>
       </c>
       <c r="C53">
-        <v>-135.3971237970361</v>
+        <v>-140.6054807891679</v>
       </c>
       <c r="D53">
-        <v>67.9998762029639</v>
+        <v>66.87851921083205</v>
       </c>
       <c r="E53">
-        <v>188.737</v>
+        <v>192.824</v>
       </c>
       <c r="F53">
-        <v>208.437</v>
+        <v>212.524</v>
       </c>
       <c r="G53">
         <v>5.04</v>
@@ -5753,37 +5753,37 @@
         <v>7.46</v>
       </c>
       <c r="M53">
-        <v>49.1494446</v>
+        <v>50.11315920000001</v>
       </c>
       <c r="N53">
-        <v>-41.6894446</v>
+        <v>-42.6531592</v>
       </c>
       <c r="O53">
-        <v>-6.0866589116</v>
+        <v>-6.2273612432</v>
       </c>
       <c r="P53">
-        <v>-35.6027856884</v>
+        <v>-36.4257979568</v>
       </c>
       <c r="Q53">
-        <v>-43.06278568840001</v>
+        <v>-43.8857979568</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08474341451855875</v>
+        <v>0.08555473565436206</v>
       </c>
       <c r="T53">
-        <v>0.8993860165948904</v>
+        <v>0.9181232252739506</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02216016902864452</v>
+        <v>0.02173401193193982</v>
       </c>
       <c r="W53">
-        <v>0.2305746321430456</v>
+        <v>0.2306751199864486</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1517819796482502</v>
+        <v>0.1488630954242454</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1610173355070471</v>
+        <v>0.1629173355070471</v>
       </c>
       <c r="C54">
-        <v>-140.6054807891679</v>
+        <v>-145.7774541276618</v>
       </c>
       <c r="D54">
-        <v>66.87851921083205</v>
+        <v>65.79354587233821</v>
       </c>
       <c r="E54">
-        <v>192.824</v>
+        <v>196.911</v>
       </c>
       <c r="F54">
-        <v>212.524</v>
+        <v>216.611</v>
       </c>
       <c r="G54">
         <v>5.04</v>
@@ -5835,37 +5835,37 @@
         <v>7.46</v>
       </c>
       <c r="M54">
-        <v>50.11315920000001</v>
+        <v>51.07687380000001</v>
       </c>
       <c r="N54">
-        <v>-42.6531592</v>
+        <v>-43.61687380000001</v>
       </c>
       <c r="O54">
-        <v>-6.2273612432</v>
+        <v>-6.368063574800001</v>
       </c>
       <c r="P54">
-        <v>-36.4257979568</v>
+        <v>-37.2488102252</v>
       </c>
       <c r="Q54">
-        <v>-43.8857979568</v>
+        <v>-44.7088102252</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08555473565436206</v>
+        <v>0.08640058109381658</v>
       </c>
       <c r="T54">
-        <v>0.9181232252739506</v>
+        <v>0.9376577619819072</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02173401193193982</v>
+        <v>0.02132393623511077</v>
       </c>
       <c r="W54">
-        <v>0.2306751199864486</v>
+        <v>0.2307718158357609</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1488630954242454</v>
+        <v>0.1460543577747313</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5881,22 +5881,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1629173355070471</v>
+        <v>0.1648173355070471</v>
       </c>
       <c r="C55">
-        <v>-145.7774541276618</v>
+        <v>-150.914786305112</v>
       </c>
       <c r="D55">
-        <v>65.79354587233821</v>
+        <v>64.74321369488798</v>
       </c>
       <c r="E55">
-        <v>196.911</v>
+        <v>200.998</v>
       </c>
       <c r="F55">
-        <v>216.611</v>
+        <v>220.698</v>
       </c>
       <c r="G55">
         <v>5.04</v>
@@ -5917,37 +5917,37 @@
         <v>7.46</v>
       </c>
       <c r="M55">
-        <v>51.07687380000001</v>
+        <v>52.0405884</v>
       </c>
       <c r="N55">
-        <v>-43.61687380000001</v>
+        <v>-44.5805884</v>
       </c>
       <c r="O55">
-        <v>-6.368063574800001</v>
+        <v>-6.5087659064</v>
       </c>
       <c r="P55">
-        <v>-37.2488102252</v>
+        <v>-38.0718224936</v>
       </c>
       <c r="Q55">
-        <v>-44.7088102252</v>
+        <v>-45.5318224936</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08640058109381658</v>
+        <v>0.08728320242194303</v>
       </c>
       <c r="T55">
-        <v>0.9376577619819072</v>
+        <v>0.9580416263728182</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02132393623511077</v>
+        <v>0.02092904852705316</v>
       </c>
       <c r="W55">
-        <v>0.2307718158357609</v>
+        <v>0.2308649303573209</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1460543577747313</v>
+        <v>0.1433496474455697</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5963,22 +5963,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1648173355070471</v>
+        <v>0.1667173355070471</v>
       </c>
       <c r="C56">
-        <v>-150.914786305112</v>
+        <v>-156.0191102934753</v>
       </c>
       <c r="D56">
-        <v>64.74321369488798</v>
+        <v>63.7258897065247</v>
       </c>
       <c r="E56">
-        <v>200.998</v>
+        <v>205.085</v>
       </c>
       <c r="F56">
-        <v>220.698</v>
+        <v>224.785</v>
       </c>
       <c r="G56">
         <v>5.04</v>
@@ -5999,37 +5999,37 @@
         <v>7.46</v>
       </c>
       <c r="M56">
-        <v>52.0405884</v>
+        <v>53.00430300000001</v>
       </c>
       <c r="N56">
-        <v>-44.5805884</v>
+        <v>-45.54430300000001</v>
       </c>
       <c r="O56">
-        <v>-6.5087659064</v>
+        <v>-6.649468238000001</v>
       </c>
       <c r="P56">
-        <v>-38.0718224936</v>
+        <v>-38.894834762</v>
       </c>
       <c r="Q56">
-        <v>-45.5318224936</v>
+        <v>-46.354834762</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08728320242194303</v>
+        <v>0.08820505136465287</v>
       </c>
       <c r="T56">
-        <v>0.9580416263728182</v>
+        <v>0.9793314402922142</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02092904852705316</v>
+        <v>0.02054852037201583</v>
       </c>
       <c r="W56">
-        <v>0.2308649303573209</v>
+        <v>0.2309546588962787</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1433496474455697</v>
+        <v>0.1407432902192866</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6045,22 +6045,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1667173355070471</v>
+        <v>0.1686173355070471</v>
       </c>
       <c r="C57">
-        <v>-156.0191102934753</v>
+        <v>-161.0919580155621</v>
       </c>
       <c r="D57">
-        <v>63.7258897065247</v>
+        <v>62.74004198443789</v>
       </c>
       <c r="E57">
-        <v>205.085</v>
+        <v>209.172</v>
       </c>
       <c r="F57">
-        <v>224.785</v>
+        <v>228.872</v>
       </c>
       <c r="G57">
         <v>5.04</v>
@@ -6081,37 +6081,37 @@
         <v>7.46</v>
       </c>
       <c r="M57">
-        <v>53.00430300000001</v>
+        <v>53.9680176</v>
       </c>
       <c r="N57">
-        <v>-45.54430300000001</v>
+        <v>-46.5080176</v>
       </c>
       <c r="O57">
-        <v>-6.649468238000001</v>
+        <v>-6.7901705696</v>
       </c>
       <c r="P57">
-        <v>-38.894834762</v>
+        <v>-39.7178470304</v>
       </c>
       <c r="Q57">
-        <v>-46.354834762</v>
+        <v>-47.1778470304</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08820505136465287</v>
+        <v>0.08916880253203134</v>
       </c>
       <c r="T57">
-        <v>0.9793314402922142</v>
+        <v>1.001588973026128</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02054852037201583</v>
+        <v>0.02018158250822983</v>
       </c>
       <c r="W57">
-        <v>0.2309546588962787</v>
+        <v>0.2310411828445594</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1407432902192866</v>
+        <v>0.1382300171796564</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6127,22 +6127,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1686173355070471</v>
+        <v>0.1705173355070471</v>
       </c>
       <c r="C58">
-        <v>-161.0919580155621</v>
+        <v>-166.1347680421779</v>
       </c>
       <c r="D58">
-        <v>62.74004198443789</v>
+        <v>61.78423195782216</v>
       </c>
       <c r="E58">
-        <v>209.172</v>
+        <v>213.259</v>
       </c>
       <c r="F58">
-        <v>228.872</v>
+        <v>232.959</v>
       </c>
       <c r="G58">
         <v>5.04</v>
@@ -6163,37 +6163,37 @@
         <v>7.46</v>
       </c>
       <c r="M58">
-        <v>53.9680176</v>
+        <v>54.93173220000001</v>
       </c>
       <c r="N58">
-        <v>-46.5080176</v>
+        <v>-47.47173220000001</v>
       </c>
       <c r="O58">
-        <v>-6.7901705696</v>
+        <v>-6.930872901200002</v>
       </c>
       <c r="P58">
-        <v>-39.7178470304</v>
+        <v>-40.54085929880001</v>
       </c>
       <c r="Q58">
-        <v>-47.1778470304</v>
+        <v>-48.00085929880001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08916880253203134</v>
+        <v>0.09017737933510184</v>
       </c>
       <c r="T58">
-        <v>1.001588973026128</v>
+        <v>1.024881739840689</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02018158250822983</v>
+        <v>0.01982751965720825</v>
       </c>
       <c r="W58">
-        <v>0.2310411828445594</v>
+        <v>0.2311246708648303</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1382300171796564</v>
+        <v>0.1358049291589607</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6209,22 +6209,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1705173355070471</v>
+        <v>0.1724173355070471</v>
       </c>
       <c r="C59">
-        <v>-166.1347680421779</v>
+        <v>-171.1488925962507</v>
       </c>
       <c r="D59">
-        <v>61.78423195782216</v>
+        <v>60.85710740374932</v>
       </c>
       <c r="E59">
-        <v>213.259</v>
+        <v>217.346</v>
       </c>
       <c r="F59">
-        <v>232.959</v>
+        <v>237.046</v>
       </c>
       <c r="G59">
         <v>5.04</v>
@@ -6245,37 +6245,37 @@
         <v>7.46</v>
       </c>
       <c r="M59">
-        <v>54.93173220000001</v>
+        <v>55.89544680000001</v>
       </c>
       <c r="N59">
-        <v>-47.47173220000001</v>
+        <v>-48.43544680000001</v>
       </c>
       <c r="O59">
-        <v>-6.930872901200002</v>
+        <v>-7.071575232800001</v>
       </c>
       <c r="P59">
-        <v>-40.54085929880001</v>
+        <v>-41.36387156720001</v>
       </c>
       <c r="Q59">
-        <v>-48.00085929880001</v>
+        <v>-48.82387156720001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09017737933510184</v>
+        <v>0.09123398360498522</v>
       </c>
       <c r="T59">
-        <v>1.024881739840689</v>
+        <v>1.049283686027372</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01982751965720825</v>
+        <v>0.01948566587001501</v>
       </c>
       <c r="W59">
-        <v>0.2311246708648303</v>
+        <v>0.2312052799878505</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1358049291589607</v>
+        <v>0.1334634648631166</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6291,22 +6291,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1724173355070471</v>
+        <v>0.1743173355070471</v>
       </c>
       <c r="C60">
-        <v>-171.1488925962506</v>
+        <v>-176.1356039356659</v>
       </c>
       <c r="D60">
-        <v>60.85710740374932</v>
+        <v>59.95739606433411</v>
       </c>
       <c r="E60">
-        <v>217.346</v>
+        <v>221.433</v>
       </c>
       <c r="F60">
-        <v>237.046</v>
+        <v>241.133</v>
       </c>
       <c r="G60">
         <v>5.04</v>
@@ -6327,37 +6327,37 @@
         <v>7.46</v>
       </c>
       <c r="M60">
-        <v>55.89544679999999</v>
+        <v>56.8591614</v>
       </c>
       <c r="N60">
-        <v>-48.43544679999999</v>
+        <v>-49.3991614</v>
       </c>
       <c r="O60">
-        <v>-7.071575232799999</v>
+        <v>-7.212277564399999</v>
       </c>
       <c r="P60">
-        <v>-41.36387156719999</v>
+        <v>-42.1868838356</v>
       </c>
       <c r="Q60">
-        <v>-48.82387156719999</v>
+        <v>-49.6468838356</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09123398360498522</v>
+        <v>0.09234212954657023</v>
       </c>
       <c r="T60">
-        <v>1.049283686027372</v>
+        <v>1.07487597105243</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01948566587001501</v>
+        <v>0.01915540034679442</v>
       </c>
       <c r="W60">
-        <v>0.2312052799878505</v>
+        <v>0.2312831565982259</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1334634648631166</v>
+        <v>0.131201372238318</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6373,22 +6373,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1743173355070471</v>
+        <v>0.176217335507047</v>
       </c>
       <c r="C61">
-        <v>-176.1356039356659</v>
+        <v>-181.0961001781656</v>
       </c>
       <c r="D61">
-        <v>59.95739606433411</v>
+        <v>59.08389982183434</v>
       </c>
       <c r="E61">
-        <v>221.433</v>
+        <v>225.52</v>
       </c>
       <c r="F61">
-        <v>241.133</v>
+        <v>245.22</v>
       </c>
       <c r="G61">
         <v>5.04</v>
@@ -6409,37 +6409,37 @@
         <v>7.46</v>
       </c>
       <c r="M61">
-        <v>56.8591614</v>
+        <v>57.82287599999999</v>
       </c>
       <c r="N61">
-        <v>-49.3991614</v>
+        <v>-50.36287599999999</v>
       </c>
       <c r="O61">
-        <v>-7.212277564399999</v>
+        <v>-7.352979895999998</v>
       </c>
       <c r="P61">
-        <v>-42.1868838356</v>
+        <v>-43.00989610399999</v>
       </c>
       <c r="Q61">
-        <v>-49.6468838356</v>
+        <v>-50.46989610399999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09234212954657023</v>
+        <v>0.09350568278523447</v>
       </c>
       <c r="T61">
-        <v>1.07487597105243</v>
+        <v>1.101747870328741</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01915540034679442</v>
+        <v>0.01883614367434785</v>
       </c>
       <c r="W61">
-        <v>0.2312831565982259</v>
+        <v>0.2313584373215888</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.131201372238318</v>
+        <v>0.1290146827010127</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6455,22 +6455,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.176217335507047</v>
+        <v>0.1781173355070471</v>
       </c>
       <c r="C62">
-        <v>-181.0961001781656</v>
+        <v>-186.0315106243955</v>
       </c>
       <c r="D62">
-        <v>59.08389982183434</v>
+        <v>58.23548937560444</v>
       </c>
       <c r="E62">
-        <v>225.52</v>
+        <v>229.607</v>
       </c>
       <c r="F62">
-        <v>245.22</v>
+        <v>249.307</v>
       </c>
       <c r="G62">
         <v>5.04</v>
@@ -6491,37 +6491,37 @@
         <v>7.46</v>
       </c>
       <c r="M62">
-        <v>57.82287599999999</v>
+        <v>58.7865906</v>
       </c>
       <c r="N62">
-        <v>-50.36287599999999</v>
+        <v>-51.3265906</v>
       </c>
       <c r="O62">
-        <v>-7.352979895999998</v>
+        <v>-7.493682227599999</v>
       </c>
       <c r="P62">
-        <v>-43.00989610399999</v>
+        <v>-43.8329083724</v>
       </c>
       <c r="Q62">
-        <v>-50.46989610399999</v>
+        <v>-51.2929083724</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09350568278523447</v>
+        <v>0.0947289054207533</v>
       </c>
       <c r="T62">
-        <v>1.101747870328741</v>
+        <v>1.129997815721785</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01883614367434785</v>
+        <v>0.01852735443378477</v>
       </c>
       <c r="W62">
-        <v>0.2313584373215888</v>
+        <v>0.2314312498245136</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1290146827010127</v>
+        <v>0.1268996879026354</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6537,22 +6537,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1781173355070471</v>
+        <v>0.1800173355070471</v>
       </c>
       <c r="C63">
-        <v>-186.0315106243955</v>
+        <v>-190.9429006288286</v>
       </c>
       <c r="D63">
-        <v>58.23548937560444</v>
+        <v>57.41109937117135</v>
       </c>
       <c r="E63">
-        <v>229.607</v>
+        <v>233.694</v>
       </c>
       <c r="F63">
-        <v>249.307</v>
+        <v>253.394</v>
       </c>
       <c r="G63">
         <v>5.04</v>
@@ -6573,37 +6573,37 @@
         <v>7.46</v>
       </c>
       <c r="M63">
-        <v>58.7865906</v>
+        <v>59.7503052</v>
       </c>
       <c r="N63">
-        <v>-51.3265906</v>
+        <v>-52.2903052</v>
       </c>
       <c r="O63">
-        <v>-7.493682227599999</v>
+        <v>-7.634384559199999</v>
       </c>
       <c r="P63">
-        <v>-43.8329083724</v>
+        <v>-44.6559206408</v>
       </c>
       <c r="Q63">
-        <v>-51.2929083724</v>
+        <v>-52.1159206408</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.0947289054207533</v>
+        <v>0.09601650819498365</v>
       </c>
       <c r="T63">
-        <v>1.129997815721785</v>
+        <v>1.159734600346043</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01852735443378477</v>
+        <v>0.01822852613646566</v>
       </c>
       <c r="W63">
-        <v>0.2314312498245136</v>
+        <v>0.2315017135370214</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1268996879026354</v>
+        <v>0.1248529187429155</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6619,22 +6619,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1800173355070471</v>
+        <v>0.1819173355070471</v>
       </c>
       <c r="C64">
-        <v>-190.9429006288286</v>
+        <v>-195.831276062743</v>
       </c>
       <c r="D64">
-        <v>57.41109937117135</v>
+        <v>56.60972393725702</v>
       </c>
       <c r="E64">
-        <v>233.694</v>
+        <v>237.781</v>
       </c>
       <c r="F64">
-        <v>253.394</v>
+        <v>257.481</v>
       </c>
       <c r="G64">
         <v>5.04</v>
@@ -6655,37 +6655,37 @@
         <v>7.46</v>
       </c>
       <c r="M64">
-        <v>59.7503052</v>
+        <v>60.7140198</v>
       </c>
       <c r="N64">
-        <v>-52.2903052</v>
+        <v>-53.2540198</v>
       </c>
       <c r="O64">
-        <v>-7.634384559199999</v>
+        <v>-7.7750868908</v>
       </c>
       <c r="P64">
-        <v>-44.6559206408</v>
+        <v>-45.4789329092</v>
       </c>
       <c r="Q64">
-        <v>-52.1159206408</v>
+        <v>-52.93893290920001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09601650819498365</v>
+        <v>0.0973737111191724</v>
       </c>
       <c r="T64">
-        <v>1.159734600346043</v>
+        <v>1.191078778733774</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01822852613646566</v>
+        <v>0.01793918445175985</v>
       </c>
       <c r="W64">
-        <v>0.2315017135370214</v>
+        <v>0.231569940306275</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1248529187429155</v>
+        <v>0.1228711263819168</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6701,22 +6701,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1819173355070471</v>
+        <v>0.183817335507047</v>
       </c>
       <c r="C65">
-        <v>-195.831276062743</v>
+        <v>-200.6975874085651</v>
       </c>
       <c r="D65">
-        <v>56.60972393725702</v>
+        <v>55.83041259143486</v>
       </c>
       <c r="E65">
-        <v>237.781</v>
+        <v>241.868</v>
       </c>
       <c r="F65">
-        <v>257.481</v>
+        <v>261.568</v>
       </c>
       <c r="G65">
         <v>5.04</v>
@@ -6737,37 +6737,37 @@
         <v>7.46</v>
       </c>
       <c r="M65">
-        <v>60.7140198</v>
+        <v>61.6777344</v>
       </c>
       <c r="N65">
-        <v>-53.2540198</v>
+        <v>-54.2177344</v>
       </c>
       <c r="O65">
-        <v>-7.7750868908</v>
+        <v>-7.915789222399999</v>
       </c>
       <c r="P65">
-        <v>-45.4789329092</v>
+        <v>-46.3019451776</v>
       </c>
       <c r="Q65">
-        <v>-52.93893290920001</v>
+        <v>-53.7619451776</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.0973737111191724</v>
+        <v>0.09880631420581609</v>
       </c>
       <c r="T65">
-        <v>1.191078778733774</v>
+        <v>1.224164300365268</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01793918445175985</v>
+        <v>0.01765888469470111</v>
       </c>
       <c r="W65">
-        <v>0.231569940306275</v>
+        <v>0.2316360349889895</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1228711263819168</v>
+        <v>0.1209512650321993</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6783,22 +6783,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.183817335507047</v>
+        <v>0.1857173355070471</v>
       </c>
       <c r="C66">
-        <v>-200.6975874085651</v>
+        <v>-205.5427335206199</v>
       </c>
       <c r="D66">
-        <v>55.83041259143486</v>
+        <v>55.07226647938009</v>
       </c>
       <c r="E66">
-        <v>241.868</v>
+        <v>245.955</v>
       </c>
       <c r="F66">
-        <v>261.568</v>
+        <v>265.655</v>
       </c>
       <c r="G66">
         <v>5.04</v>
@@ -6819,37 +6819,37 @@
         <v>7.46</v>
       </c>
       <c r="M66">
-        <v>61.6777344</v>
+        <v>62.64144900000001</v>
       </c>
       <c r="N66">
-        <v>-54.2177344</v>
+        <v>-55.18144900000001</v>
       </c>
       <c r="O66">
-        <v>-7.915789222399999</v>
+        <v>-8.056491554000001</v>
       </c>
       <c r="P66">
-        <v>-46.3019451776</v>
+        <v>-47.12495744600001</v>
       </c>
       <c r="Q66">
-        <v>-53.7619451776</v>
+        <v>-54.58495744600001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09880631420581609</v>
+        <v>0.1003207803259823</v>
       </c>
       <c r="T66">
-        <v>1.224164300365268</v>
+        <v>1.259140423232847</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01765888469470111</v>
+        <v>0.01738720954555186</v>
       </c>
       <c r="W66">
-        <v>0.2316360349889895</v>
+        <v>0.2317000959891589</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1209512650321993</v>
+        <v>0.1190904763393963</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1857173355070471</v>
+        <v>0.1876173355070471</v>
       </c>
       <c r="C67">
-        <v>-205.5427335206199</v>
+        <v>-210.3675650835717</v>
       </c>
       <c r="D67">
-        <v>55.07226647938009</v>
+        <v>54.33443491642833</v>
       </c>
       <c r="E67">
-        <v>245.955</v>
+        <v>250.042</v>
       </c>
       <c r="F67">
-        <v>265.655</v>
+        <v>269.742</v>
       </c>
       <c r="G67">
         <v>5.04</v>
@@ -6901,37 +6901,37 @@
         <v>7.46</v>
       </c>
       <c r="M67">
-        <v>62.64144900000001</v>
+        <v>63.6051636</v>
       </c>
       <c r="N67">
-        <v>-55.18144900000001</v>
+        <v>-56.1451636</v>
       </c>
       <c r="O67">
-        <v>-8.056491554000001</v>
+        <v>-8.197193885600001</v>
       </c>
       <c r="P67">
-        <v>-47.12495744600001</v>
+        <v>-47.9479697144</v>
       </c>
       <c r="Q67">
-        <v>-54.58495744600001</v>
+        <v>-55.4079697144</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1003207803259823</v>
+        <v>0.1019243326885111</v>
       </c>
       <c r="T67">
-        <v>1.259140423232847</v>
+        <v>1.296173965092636</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01738720954555186</v>
+        <v>0.01712376697667986</v>
       </c>
       <c r="W67">
-        <v>0.2317000959891589</v>
+        <v>0.2317622157468989</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1190904763393963</v>
+        <v>0.1172860751827388</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6947,22 +6947,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1876173355070471</v>
+        <v>0.1895173355070471</v>
       </c>
       <c r="C68">
-        <v>-210.3675650835717</v>
+        <v>-215.1728877965346</v>
       </c>
       <c r="D68">
-        <v>54.33443491642833</v>
+        <v>53.61611220346545</v>
       </c>
       <c r="E68">
-        <v>250.042</v>
+        <v>254.129</v>
       </c>
       <c r="F68">
-        <v>269.742</v>
+        <v>273.829</v>
       </c>
       <c r="G68">
         <v>5.04</v>
@@ -6983,37 +6983,37 @@
         <v>7.46</v>
       </c>
       <c r="M68">
-        <v>63.6051636</v>
+        <v>64.5688782</v>
       </c>
       <c r="N68">
-        <v>-56.1451636</v>
+        <v>-57.1088782</v>
       </c>
       <c r="O68">
-        <v>-8.197193885600001</v>
+        <v>-8.337896217199999</v>
       </c>
       <c r="P68">
-        <v>-47.9479697144</v>
+        <v>-48.7709819828</v>
       </c>
       <c r="Q68">
-        <v>-55.4079697144</v>
+        <v>-56.2309819828</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1019243326885111</v>
+        <v>0.1036250700427085</v>
       </c>
       <c r="T68">
-        <v>1.296173965092636</v>
+        <v>1.335451964034837</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01712376697667986</v>
+        <v>0.01686818836508762</v>
       </c>
       <c r="W68">
-        <v>0.2317622157468989</v>
+        <v>0.2318224811835123</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1172860751827388</v>
+        <v>0.1155355367471755</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7029,22 +7029,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1895173355070471</v>
+        <v>0.1914173355070471</v>
       </c>
       <c r="C69">
-        <v>-215.1728877965346</v>
+        <v>-219.9594653079061</v>
       </c>
       <c r="D69">
-        <v>53.61611220346545</v>
+        <v>52.91653469209387</v>
       </c>
       <c r="E69">
-        <v>254.129</v>
+        <v>258.216</v>
       </c>
       <c r="F69">
-        <v>273.829</v>
+        <v>277.916</v>
       </c>
       <c r="G69">
         <v>5.04</v>
@@ -7065,37 +7065,37 @@
         <v>7.46</v>
       </c>
       <c r="M69">
-        <v>64.5688782</v>
+        <v>65.5325928</v>
       </c>
       <c r="N69">
-        <v>-57.1088782</v>
+        <v>-58.0725928</v>
       </c>
       <c r="O69">
-        <v>-8.337896217199999</v>
+        <v>-8.478598548799999</v>
       </c>
       <c r="P69">
-        <v>-48.7709819828</v>
+        <v>-49.5939942512</v>
       </c>
       <c r="Q69">
-        <v>-56.2309819828</v>
+        <v>-57.0539942512</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1036250700427085</v>
+        <v>0.1054321034815431</v>
       </c>
       <c r="T69">
-        <v>1.335451964034837</v>
+        <v>1.377184837910926</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01686818836508762</v>
+        <v>0.01662012677148339</v>
       </c>
       <c r="W69">
-        <v>0.2318224811835123</v>
+        <v>0.2318809741072842</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1155355367471755</v>
+        <v>0.1138364847361877</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7111,22 +7111,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1914173355070471</v>
+        <v>0.1933173355070471</v>
       </c>
       <c r="C70">
-        <v>-219.9594653079061</v>
+        <v>-224.7280219234009</v>
       </c>
       <c r="D70">
-        <v>52.91653469209387</v>
+        <v>52.23497807659911</v>
       </c>
       <c r="E70">
-        <v>258.216</v>
+        <v>262.3030000000001</v>
       </c>
       <c r="F70">
-        <v>277.916</v>
+        <v>282.003</v>
       </c>
       <c r="G70">
         <v>5.04</v>
@@ -7147,37 +7147,37 @@
         <v>7.46</v>
       </c>
       <c r="M70">
-        <v>65.5325928</v>
+        <v>66.49630740000001</v>
       </c>
       <c r="N70">
-        <v>-58.0725928</v>
+        <v>-59.03630740000001</v>
       </c>
       <c r="O70">
-        <v>-8.478598548799999</v>
+        <v>-8.619300880400001</v>
       </c>
       <c r="P70">
-        <v>-49.5939942512</v>
+        <v>-50.41700651960001</v>
       </c>
       <c r="Q70">
-        <v>-57.0539942512</v>
+        <v>-57.87700651960001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1054321034815431</v>
+        <v>0.1073557197228832</v>
       </c>
       <c r="T70">
-        <v>1.377184837910926</v>
+        <v>1.421610155262892</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01662012677148339</v>
+        <v>0.01637925536899813</v>
       </c>
       <c r="W70">
-        <v>0.2318809741072842</v>
+        <v>0.2319377715839903</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1138364847361877</v>
+        <v>0.1121866806095763</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7193,22 +7193,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1933173355070471</v>
+        <v>0.1952173355070471</v>
       </c>
       <c r="C71">
-        <v>-224.7280219234009</v>
+        <v>-229.4792451074695</v>
       </c>
       <c r="D71">
-        <v>52.23497807659911</v>
+        <v>51.57075489253058</v>
       </c>
       <c r="E71">
-        <v>262.3030000000001</v>
+        <v>266.39</v>
       </c>
       <c r="F71">
-        <v>282.003</v>
+        <v>286.09</v>
       </c>
       <c r="G71">
         <v>5.04</v>
@@ -7229,37 +7229,37 @@
         <v>7.46</v>
       </c>
       <c r="M71">
-        <v>66.49630740000001</v>
+        <v>67.46002200000001</v>
       </c>
       <c r="N71">
-        <v>-59.03630740000001</v>
+        <v>-60.00002200000001</v>
       </c>
       <c r="O71">
-        <v>-8.619300880400001</v>
+        <v>-8.760003212000001</v>
       </c>
       <c r="P71">
-        <v>-50.41700651960001</v>
+        <v>-51.24001878800001</v>
       </c>
       <c r="Q71">
-        <v>-57.87700651960001</v>
+        <v>-58.70001878800001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1073557197228832</v>
+        <v>0.1094075770469793</v>
       </c>
       <c r="T71">
-        <v>1.421610155262892</v>
+        <v>1.468997160438321</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01637925536899813</v>
+        <v>0.01614526600658387</v>
       </c>
       <c r="W71">
-        <v>0.2319377715839903</v>
+        <v>0.2319929462756475</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1121866806095763</v>
+        <v>0.1105840137437252</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7275,22 +7275,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1952173355070471</v>
+        <v>0.1971173355070471</v>
       </c>
       <c r="C72">
-        <v>-229.4792451074695</v>
+        <v>-234.2137877962663</v>
       </c>
       <c r="D72">
-        <v>51.57075489253058</v>
+        <v>50.92321220373373</v>
       </c>
       <c r="E72">
-        <v>266.39</v>
+        <v>270.477</v>
       </c>
       <c r="F72">
-        <v>286.09</v>
+        <v>290.177</v>
       </c>
       <c r="G72">
         <v>5.04</v>
@@ -7311,37 +7311,37 @@
         <v>7.46</v>
       </c>
       <c r="M72">
-        <v>67.46002200000001</v>
+        <v>68.42373660000001</v>
       </c>
       <c r="N72">
-        <v>-60.00002200000001</v>
+        <v>-60.96373660000001</v>
       </c>
       <c r="O72">
-        <v>-8.760003212000001</v>
+        <v>-8.900705543600001</v>
       </c>
       <c r="P72">
-        <v>-51.24001878800001</v>
+        <v>-52.06303105640001</v>
       </c>
       <c r="Q72">
-        <v>-58.70001878800001</v>
+        <v>-59.52303105640001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1094075770469793</v>
+        <v>0.1116009417727372</v>
       </c>
       <c r="T72">
-        <v>1.468997160438321</v>
+        <v>1.519652234936195</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01614526600658387</v>
+        <v>0.01591786789381508</v>
       </c>
       <c r="W72">
-        <v>0.2319929462756475</v>
+        <v>0.2320465667506384</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1105840137437252</v>
+        <v>0.109026492423391</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7357,22 +7357,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.197117335507047</v>
+        <v>0.199017335507047</v>
       </c>
       <c r="C73">
-        <v>-234.2137877962663</v>
+        <v>-238.9322705385218</v>
       </c>
       <c r="D73">
-        <v>50.92321220373368</v>
+        <v>50.29172946147811</v>
       </c>
       <c r="E73">
-        <v>270.477</v>
+        <v>274.564</v>
       </c>
       <c r="F73">
-        <v>290.177</v>
+        <v>294.264</v>
       </c>
       <c r="G73">
         <v>5.04</v>
@@ -7393,37 +7393,37 @@
         <v>7.46</v>
       </c>
       <c r="M73">
-        <v>68.4237366</v>
+        <v>69.38745119999999</v>
       </c>
       <c r="N73">
-        <v>-60.9637366</v>
+        <v>-61.92745119999999</v>
       </c>
       <c r="O73">
-        <v>-8.900705543599999</v>
+        <v>-9.041407875199997</v>
       </c>
       <c r="P73">
-        <v>-52.0630310564</v>
+        <v>-52.88604332479999</v>
       </c>
       <c r="Q73">
-        <v>-59.5230310564</v>
+        <v>-60.34604332479999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1116009417727372</v>
+        <v>0.1139509754074778</v>
       </c>
       <c r="T73">
-        <v>1.519652234936194</v>
+        <v>1.573925529041058</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01591786789381508</v>
+        <v>0.01569678639528987</v>
       </c>
       <c r="W73">
-        <v>0.2320465667506384</v>
+        <v>0.2320986977679906</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.109026492423391</v>
+        <v>0.1075122355841772</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7439,22 +7439,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.199017335507047</v>
+        <v>0.200917335507047</v>
       </c>
       <c r="C74">
-        <v>-238.9322705385218</v>
+        <v>-243.6352834790773</v>
       </c>
       <c r="D74">
-        <v>50.29172946147811</v>
+        <v>49.67571652092273</v>
       </c>
       <c r="E74">
-        <v>274.564</v>
+        <v>278.651</v>
       </c>
       <c r="F74">
-        <v>294.264</v>
+        <v>298.351</v>
       </c>
       <c r="G74">
         <v>5.04</v>
@@ -7475,37 +7475,37 @@
         <v>7.46</v>
       </c>
       <c r="M74">
-        <v>69.38745119999999</v>
+        <v>70.3511658</v>
       </c>
       <c r="N74">
-        <v>-61.92745119999999</v>
+        <v>-62.8911658</v>
       </c>
       <c r="O74">
-        <v>-9.041407875199997</v>
+        <v>-9.182110206799999</v>
       </c>
       <c r="P74">
-        <v>-52.88604332479999</v>
+        <v>-53.70905559320001</v>
       </c>
       <c r="Q74">
-        <v>-60.34604332479999</v>
+        <v>-61.16905559320001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1139509754074778</v>
+        <v>0.1164750856077548</v>
       </c>
       <c r="T74">
-        <v>1.573925529041058</v>
+        <v>1.63221906715369</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01569678639528987</v>
+        <v>0.01548176192412152</v>
       </c>
       <c r="W74">
-        <v>0.2320986977679906</v>
+        <v>0.2321494005382921</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1075122355841772</v>
+        <v>0.106039465233709</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7521,22 +7521,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.200917335507047</v>
+        <v>0.2028173355070471</v>
       </c>
       <c r="C75">
-        <v>-243.6352834790773</v>
+        <v>-248.3233881984063</v>
       </c>
       <c r="D75">
-        <v>49.67571652092273</v>
+        <v>49.07461180159363</v>
       </c>
       <c r="E75">
-        <v>278.651</v>
+        <v>282.738</v>
       </c>
       <c r="F75">
-        <v>298.351</v>
+        <v>302.438</v>
       </c>
       <c r="G75">
         <v>5.04</v>
@@ -7557,37 +7557,37 @@
         <v>7.46</v>
       </c>
       <c r="M75">
-        <v>70.3511658</v>
+        <v>71.31488040000001</v>
       </c>
       <c r="N75">
-        <v>-62.8911658</v>
+        <v>-63.85488040000001</v>
       </c>
       <c r="O75">
-        <v>-9.182110206799999</v>
+        <v>-9.322812538400001</v>
       </c>
       <c r="P75">
-        <v>-53.70905559320001</v>
+        <v>-54.53206786160001</v>
       </c>
       <c r="Q75">
-        <v>-61.16905559320001</v>
+        <v>-61.99206786160001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1164750856077548</v>
+        <v>0.11919335813113</v>
       </c>
       <c r="T75">
-        <v>1.63221906715369</v>
+        <v>1.694996723582678</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01548176192412152</v>
+        <v>0.0152725489251469</v>
       </c>
       <c r="W75">
-        <v>0.2321494005382921</v>
+        <v>0.2321987329634504</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.106039465233709</v>
+        <v>0.1046064994873076</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7603,22 +7603,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2028173355070471</v>
+        <v>0.2047173355070471</v>
       </c>
       <c r="C76">
-        <v>-248.3233881984063</v>
+        <v>-252.9971194201797</v>
       </c>
       <c r="D76">
-        <v>49.07461180159363</v>
+        <v>48.48788057982028</v>
       </c>
       <c r="E76">
-        <v>282.738</v>
+        <v>286.825</v>
       </c>
       <c r="F76">
-        <v>302.438</v>
+        <v>306.525</v>
       </c>
       <c r="G76">
         <v>5.04</v>
@@ -7639,37 +7639,37 @@
         <v>7.46</v>
       </c>
       <c r="M76">
-        <v>71.31488040000001</v>
+        <v>72.278595</v>
       </c>
       <c r="N76">
-        <v>-63.85488040000001</v>
+        <v>-64.818595</v>
       </c>
       <c r="O76">
-        <v>-9.322812538400001</v>
+        <v>-9.463514869999999</v>
       </c>
       <c r="P76">
-        <v>-54.53206786160001</v>
+        <v>-55.35508013</v>
       </c>
       <c r="Q76">
-        <v>-61.99206786160001</v>
+        <v>-62.81508013000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.11919335813113</v>
+        <v>0.1221290924563752</v>
       </c>
       <c r="T76">
-        <v>1.694996723582678</v>
+        <v>1.762796592525985</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0152725489251469</v>
+        <v>0.01506891493947828</v>
       </c>
       <c r="W76">
-        <v>0.2321987329634504</v>
+        <v>0.232246749857271</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1046064994873076</v>
+        <v>0.1032117461608101</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7685,22 +7685,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2047173355070471</v>
+        <v>0.2066173355070471</v>
       </c>
       <c r="C77">
-        <v>-252.9971194201797</v>
+        <v>-257.6569865977834</v>
       </c>
       <c r="D77">
-        <v>48.48788057982028</v>
+        <v>47.91501340221664</v>
       </c>
       <c r="E77">
-        <v>286.825</v>
+        <v>290.912</v>
       </c>
       <c r="F77">
-        <v>306.525</v>
+        <v>310.612</v>
       </c>
       <c r="G77">
         <v>5.04</v>
@@ -7721,37 +7721,37 @@
         <v>7.46</v>
       </c>
       <c r="M77">
-        <v>72.278595</v>
+        <v>73.24230960000001</v>
       </c>
       <c r="N77">
-        <v>-64.818595</v>
+        <v>-65.78230960000002</v>
       </c>
       <c r="O77">
-        <v>-9.463514869999999</v>
+        <v>-9.604217201600003</v>
       </c>
       <c r="P77">
-        <v>-55.35508013</v>
+        <v>-56.17809239840002</v>
       </c>
       <c r="Q77">
-        <v>-62.81508013000001</v>
+        <v>-63.63809239840002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1221290924563752</v>
+        <v>0.1253094713087241</v>
       </c>
       <c r="T77">
-        <v>1.762796592525985</v>
+        <v>1.836246450547902</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01506891493947828</v>
+        <v>0.01487063974290619</v>
       </c>
       <c r="W77">
-        <v>0.232246749857271</v>
+        <v>0.2322935031486227</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1032117461608101</v>
+        <v>0.1018536968692204</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7767,22 +7767,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2066173355070471</v>
+        <v>0.2085173355070471</v>
       </c>
       <c r="C78">
-        <v>-257.6569865977834</v>
+        <v>-262.3034753896846</v>
       </c>
       <c r="D78">
-        <v>47.91501340221664</v>
+        <v>47.35552461031543</v>
       </c>
       <c r="E78">
-        <v>290.912</v>
+        <v>294.999</v>
       </c>
       <c r="F78">
-        <v>310.612</v>
+        <v>314.699</v>
       </c>
       <c r="G78">
         <v>5.04</v>
@@ -7803,37 +7803,37 @@
         <v>7.46</v>
       </c>
       <c r="M78">
-        <v>73.24230960000001</v>
+        <v>74.2060242</v>
       </c>
       <c r="N78">
-        <v>-65.78230960000002</v>
+        <v>-66.74602420000001</v>
       </c>
       <c r="O78">
-        <v>-9.604217201600003</v>
+        <v>-9.744919533200001</v>
       </c>
       <c r="P78">
-        <v>-56.17809239840002</v>
+        <v>-57.0011046668</v>
       </c>
       <c r="Q78">
-        <v>-63.63809239840002</v>
+        <v>-64.4611046668</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1253094713087241</v>
+        <v>0.128766404843886</v>
       </c>
       <c r="T78">
-        <v>1.836246450547902</v>
+        <v>1.916083252745636</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01487063974290619</v>
+        <v>0.01467751455143988</v>
       </c>
       <c r="W78">
-        <v>0.2322935031486227</v>
+        <v>0.2323390420687705</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1018536968692204</v>
+        <v>0.1005309215852046</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7849,22 +7849,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2085173355070471</v>
+        <v>0.2104173355070471</v>
       </c>
       <c r="C79">
-        <v>-262.3034753896846</v>
+        <v>-266.9370490326272</v>
       </c>
       <c r="D79">
-        <v>47.35552461031543</v>
+        <v>46.80895096737284</v>
       </c>
       <c r="E79">
-        <v>294.999</v>
+        <v>299.086</v>
       </c>
       <c r="F79">
-        <v>314.699</v>
+        <v>318.786</v>
       </c>
       <c r="G79">
         <v>5.04</v>
@@ -7885,37 +7885,37 @@
         <v>7.46</v>
       </c>
       <c r="M79">
-        <v>74.2060242</v>
+        <v>75.1697388</v>
       </c>
       <c r="N79">
-        <v>-66.74602420000001</v>
+        <v>-67.70973880000001</v>
       </c>
       <c r="O79">
-        <v>-9.744919533200001</v>
+        <v>-9.885621864800001</v>
       </c>
       <c r="P79">
-        <v>-57.0011046668</v>
+        <v>-57.82411693520001</v>
       </c>
       <c r="Q79">
-        <v>-64.4611046668</v>
+        <v>-65.2841169352</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.128766404843886</v>
+        <v>0.1325376050640627</v>
       </c>
       <c r="T79">
-        <v>1.916083252745636</v>
+        <v>2.003177946052256</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01467751455143988</v>
+        <v>0.01448934128795988</v>
       </c>
       <c r="W79">
-        <v>0.2323390420687705</v>
+        <v>0.2323834133242991</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1005309215852046</v>
+        <v>0.0992420636161635</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7931,22 +7931,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2104173355070471</v>
+        <v>0.2123173355070471</v>
       </c>
       <c r="C80">
-        <v>-266.9370490326272</v>
+        <v>-271.5581496208164</v>
       </c>
       <c r="D80">
-        <v>46.80895096737284</v>
+        <v>46.27485037918362</v>
       </c>
       <c r="E80">
-        <v>299.086</v>
+        <v>303.173</v>
       </c>
       <c r="F80">
-        <v>318.786</v>
+        <v>322.873</v>
       </c>
       <c r="G80">
         <v>5.04</v>
@@ -7967,37 +7967,37 @@
         <v>7.46</v>
       </c>
       <c r="M80">
-        <v>75.1697388</v>
+        <v>76.13345340000001</v>
       </c>
       <c r="N80">
-        <v>-67.70973880000001</v>
+        <v>-68.67345340000001</v>
       </c>
       <c r="O80">
-        <v>-9.885621864800001</v>
+        <v>-10.0263241964</v>
       </c>
       <c r="P80">
-        <v>-57.82411693520001</v>
+        <v>-58.64712920360002</v>
       </c>
       <c r="Q80">
-        <v>-65.2841169352</v>
+        <v>-66.10712920360001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1325376050640627</v>
+        <v>0.1366679672099705</v>
       </c>
       <c r="T80">
-        <v>2.003177946052256</v>
+        <v>2.098567372054745</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01448934128795988</v>
+        <v>0.01430593190456798</v>
       </c>
       <c r="W80">
-        <v>0.2323834133242991</v>
+        <v>0.2324266612569029</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0992420636161635</v>
+        <v>0.09798583496279434</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8013,22 +8013,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2123173355070471</v>
+        <v>0.2142173355070471</v>
       </c>
       <c r="C81">
-        <v>-271.5581496208164</v>
+        <v>-276.1671992985158</v>
       </c>
       <c r="D81">
-        <v>46.27485037918362</v>
+        <v>45.75280070148425</v>
       </c>
       <c r="E81">
-        <v>303.173</v>
+        <v>307.26</v>
       </c>
       <c r="F81">
-        <v>322.873</v>
+        <v>326.96</v>
       </c>
       <c r="G81">
         <v>5.04</v>
@@ -8049,37 +8049,37 @@
         <v>7.46</v>
       </c>
       <c r="M81">
-        <v>76.13345340000001</v>
+        <v>77.09716800000001</v>
       </c>
       <c r="N81">
-        <v>-68.67345340000001</v>
+        <v>-69.63716800000002</v>
       </c>
       <c r="O81">
-        <v>-10.0263241964</v>
+        <v>-10.167026528</v>
       </c>
       <c r="P81">
-        <v>-58.64712920360002</v>
+        <v>-59.47014147200002</v>
       </c>
       <c r="Q81">
-        <v>-66.10712920360001</v>
+        <v>-66.93014147200002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1366679672099705</v>
+        <v>0.141211365570469</v>
       </c>
       <c r="T81">
-        <v>2.098567372054745</v>
+        <v>2.203495740657482</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01430593190456798</v>
+        <v>0.01412710775576088</v>
       </c>
       <c r="W81">
-        <v>0.2324266612569029</v>
+        <v>0.2324688279911916</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.09798583496279434</v>
+        <v>0.09676101202575937</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8095,22 +8095,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2142173355070471</v>
+        <v>0.2161173355070471</v>
       </c>
       <c r="C82">
-        <v>-276.1671992985158</v>
+        <v>-280.7646013728204</v>
       </c>
       <c r="D82">
-        <v>45.75280070148425</v>
+        <v>45.24239862717965</v>
       </c>
       <c r="E82">
-        <v>307.26</v>
+        <v>311.347</v>
       </c>
       <c r="F82">
-        <v>326.96</v>
+        <v>331.047</v>
       </c>
       <c r="G82">
         <v>5.04</v>
@@ -8131,37 +8131,37 @@
         <v>7.46</v>
       </c>
       <c r="M82">
-        <v>77.09716800000001</v>
+        <v>78.06088260000001</v>
       </c>
       <c r="N82">
-        <v>-69.63716800000002</v>
+        <v>-70.60088260000002</v>
       </c>
       <c r="O82">
-        <v>-10.167026528</v>
+        <v>-10.3077288596</v>
       </c>
       <c r="P82">
-        <v>-59.47014147200002</v>
+        <v>-60.29315374040002</v>
       </c>
       <c r="Q82">
-        <v>-66.93014147200002</v>
+        <v>-67.75315374040001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.141211365570469</v>
+        <v>0.1462330163899674</v>
       </c>
       <c r="T82">
-        <v>2.203495740657482</v>
+        <v>2.319469200692087</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01412710775576088</v>
+        <v>0.01395269901803544</v>
       </c>
       <c r="W82">
-        <v>0.2324688279911916</v>
+        <v>0.2325099535715472</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09676101202575937</v>
+        <v>0.0955664316303797</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8177,22 +8177,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2161173355070471</v>
+        <v>0.218017335507047</v>
       </c>
       <c r="C83">
-        <v>-280.7646013728204</v>
+        <v>-285.3507413527681</v>
       </c>
       <c r="D83">
-        <v>45.24239862717965</v>
+        <v>44.74325864723196</v>
       </c>
       <c r="E83">
-        <v>311.347</v>
+        <v>315.434</v>
       </c>
       <c r="F83">
-        <v>331.047</v>
+        <v>335.134</v>
       </c>
       <c r="G83">
         <v>5.04</v>
@@ -8213,37 +8213,37 @@
         <v>7.46</v>
       </c>
       <c r="M83">
-        <v>78.06088260000001</v>
+        <v>79.0245972</v>
       </c>
       <c r="N83">
-        <v>-70.60088260000002</v>
+        <v>-71.56459720000001</v>
       </c>
       <c r="O83">
-        <v>-10.3077288596</v>
+        <v>-10.4484311912</v>
       </c>
       <c r="P83">
-        <v>-60.29315374040002</v>
+        <v>-61.11616600880001</v>
       </c>
       <c r="Q83">
-        <v>-67.75315374040001</v>
+        <v>-68.5761660088</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1462330163899674</v>
+        <v>0.1518126284116322</v>
       </c>
       <c r="T83">
-        <v>2.319469200692087</v>
+        <v>2.448328600730536</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01395269901803544</v>
+        <v>0.01378254415196184</v>
       </c>
       <c r="W83">
-        <v>0.2325099535715472</v>
+        <v>0.2325500760889674</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.0955664316303797</v>
+        <v>0.09440098734220426</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8259,22 +8259,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.218017335507047</v>
+        <v>0.2199173355070471</v>
       </c>
       <c r="C84">
-        <v>-285.3507413527681</v>
+        <v>-289.9259879204184</v>
       </c>
       <c r="D84">
-        <v>44.74325864723196</v>
+        <v>44.25501207958155</v>
       </c>
       <c r="E84">
-        <v>315.434</v>
+        <v>319.521</v>
       </c>
       <c r="F84">
-        <v>335.134</v>
+        <v>339.221</v>
       </c>
       <c r="G84">
         <v>5.04</v>
@@ -8295,37 +8295,37 @@
         <v>7.46</v>
       </c>
       <c r="M84">
-        <v>79.0245972</v>
+        <v>79.98831180000001</v>
       </c>
       <c r="N84">
-        <v>-71.56459720000001</v>
+        <v>-72.52831180000001</v>
       </c>
       <c r="O84">
-        <v>-10.4484311912</v>
+        <v>-10.5891335228</v>
       </c>
       <c r="P84">
-        <v>-61.11616600880001</v>
+        <v>-61.93917827720001</v>
       </c>
       <c r="Q84">
-        <v>-68.5761660088</v>
+        <v>-69.39917827720001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1518126284116322</v>
+        <v>0.1580486653770223</v>
       </c>
       <c r="T84">
-        <v>2.448328600730536</v>
+        <v>2.592347930185273</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01378254415196184</v>
+        <v>0.01361648940314302</v>
       </c>
       <c r="W84">
-        <v>0.2325500760889674</v>
+        <v>0.2325892317987389</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09440098734220426</v>
+        <v>0.09326362604892469</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8341,22 +8341,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2199173355070471</v>
+        <v>0.2218173355070471</v>
       </c>
       <c r="C85">
-        <v>-289.9259879204184</v>
+        <v>-294.4906938390372</v>
       </c>
       <c r="D85">
-        <v>44.25501207958155</v>
+        <v>43.77730616096285</v>
       </c>
       <c r="E85">
-        <v>319.521</v>
+        <v>323.6080000000001</v>
       </c>
       <c r="F85">
-        <v>339.221</v>
+        <v>343.308</v>
       </c>
       <c r="G85">
         <v>5.04</v>
@@ -8377,37 +8377,37 @@
         <v>7.46</v>
       </c>
       <c r="M85">
-        <v>79.98831180000001</v>
+        <v>80.95202640000001</v>
       </c>
       <c r="N85">
-        <v>-72.52831180000001</v>
+        <v>-73.49202640000001</v>
       </c>
       <c r="O85">
-        <v>-10.5891335228</v>
+        <v>-10.7298358544</v>
       </c>
       <c r="P85">
-        <v>-61.93917827720001</v>
+        <v>-62.76219054560001</v>
       </c>
       <c r="Q85">
-        <v>-69.39917827720001</v>
+        <v>-70.22219054560001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1580486653770223</v>
+        <v>0.1650642069630863</v>
       </c>
       <c r="T85">
-        <v>2.592347930185273</v>
+        <v>2.754369675821854</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01361648940314302</v>
+        <v>0.01345438833881989</v>
       </c>
       <c r="W85">
-        <v>0.2325892317987389</v>
+        <v>0.2326274552297063</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.09326362604892469</v>
+        <v>0.09215334478643755</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8423,22 +8423,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2218173355070471</v>
+        <v>0.2237173355070471</v>
       </c>
       <c r="C86">
-        <v>-294.4906938390371</v>
+        <v>-299.0451968030894</v>
       </c>
       <c r="D86">
-        <v>43.77730616096294</v>
+        <v>43.30980319691061</v>
       </c>
       <c r="E86">
-        <v>323.608</v>
+        <v>327.695</v>
       </c>
       <c r="F86">
-        <v>343.308</v>
+        <v>347.395</v>
       </c>
       <c r="G86">
         <v>5.04</v>
@@ -8459,37 +8459,37 @@
         <v>7.46</v>
       </c>
       <c r="M86">
-        <v>80.95202640000001</v>
+        <v>81.915741</v>
       </c>
       <c r="N86">
-        <v>-73.49202640000001</v>
+        <v>-74.455741</v>
       </c>
       <c r="O86">
-        <v>-10.7298358544</v>
+        <v>-10.870538186</v>
       </c>
       <c r="P86">
-        <v>-62.76219054560001</v>
+        <v>-63.58520281400001</v>
       </c>
       <c r="Q86">
-        <v>-70.22219054560001</v>
+        <v>-71.04520281400001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1650642069630862</v>
+        <v>0.1730151540939586</v>
       </c>
       <c r="T86">
-        <v>2.754369675821852</v>
+        <v>2.937994320876642</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01345438833881989</v>
+        <v>0.01329610141718672</v>
       </c>
       <c r="W86">
-        <v>0.2326274552297063</v>
+        <v>0.2326647792858274</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09215334478643755</v>
+        <v>0.09106918778895001</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8505,22 +8505,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2237173355070471</v>
+        <v>0.2256173355070471</v>
       </c>
       <c r="C87">
-        <v>-299.0451968030894</v>
+        <v>-303.5898202343458</v>
       </c>
       <c r="D87">
-        <v>43.30980319691061</v>
+        <v>42.85217976565412</v>
       </c>
       <c r="E87">
-        <v>327.695</v>
+        <v>331.782</v>
       </c>
       <c r="F87">
-        <v>347.395</v>
+        <v>351.482</v>
       </c>
       <c r="G87">
         <v>5.04</v>
@@ -8541,37 +8541,37 @@
         <v>7.46</v>
       </c>
       <c r="M87">
-        <v>81.915741</v>
+        <v>82.8794556</v>
       </c>
       <c r="N87">
-        <v>-74.455741</v>
+        <v>-75.41945560000001</v>
       </c>
       <c r="O87">
-        <v>-10.870538186</v>
+        <v>-11.0112405176</v>
       </c>
       <c r="P87">
-        <v>-63.58520281400001</v>
+        <v>-64.40821508240001</v>
       </c>
       <c r="Q87">
-        <v>-71.04520281400001</v>
+        <v>-71.8682150824</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1730151540939586</v>
+        <v>0.1821019508149556</v>
       </c>
       <c r="T87">
-        <v>2.937994320876642</v>
+        <v>3.147851058082117</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01329610141718672</v>
+        <v>0.01314149558675431</v>
       </c>
       <c r="W87">
-        <v>0.2326647792858274</v>
+        <v>0.2327012353406434</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.09106918778895001</v>
+        <v>0.09001024374489253</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8587,22 +8587,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2256173355070471</v>
+        <v>0.2275173355070471</v>
       </c>
       <c r="C88">
-        <v>-303.5898202343458</v>
+        <v>-308.1248740280445</v>
       </c>
       <c r="D88">
-        <v>42.85217976565412</v>
+        <v>42.40412597195552</v>
       </c>
       <c r="E88">
-        <v>331.782</v>
+        <v>335.869</v>
       </c>
       <c r="F88">
-        <v>351.482</v>
+        <v>355.569</v>
       </c>
       <c r="G88">
         <v>5.04</v>
@@ -8623,37 +8623,37 @@
         <v>7.46</v>
       </c>
       <c r="M88">
-        <v>82.8794556</v>
+        <v>83.84317019999999</v>
       </c>
       <c r="N88">
-        <v>-75.41945560000001</v>
+        <v>-76.3831702</v>
       </c>
       <c r="O88">
-        <v>-11.0112405176</v>
+        <v>-11.1519428492</v>
       </c>
       <c r="P88">
-        <v>-64.40821508240001</v>
+        <v>-65.2312273508</v>
       </c>
       <c r="Q88">
-        <v>-71.8682150824</v>
+        <v>-72.69122735079999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1821019508149556</v>
+        <v>0.1925867162622599</v>
       </c>
       <c r="T88">
-        <v>3.147851058082117</v>
+        <v>3.389993447165356</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01314149558675431</v>
+        <v>0.01299044391334334</v>
       </c>
       <c r="W88">
-        <v>0.2327012353406434</v>
+        <v>0.2327368533252336</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09001024374489253</v>
+        <v>0.08897564324207763</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8669,22 +8669,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2275173355070471</v>
+        <v>0.2294173355070471</v>
       </c>
       <c r="C89">
-        <v>-308.1248740280445</v>
+        <v>-312.6506552527269</v>
       </c>
       <c r="D89">
-        <v>42.40412597195552</v>
+        <v>41.96534474727304</v>
       </c>
       <c r="E89">
-        <v>335.869</v>
+        <v>339.956</v>
       </c>
       <c r="F89">
-        <v>355.569</v>
+        <v>359.656</v>
       </c>
       <c r="G89">
         <v>5.04</v>
@@ -8705,37 +8705,37 @@
         <v>7.46</v>
       </c>
       <c r="M89">
-        <v>83.84317019999999</v>
+        <v>84.80688480000001</v>
       </c>
       <c r="N89">
-        <v>-76.3831702</v>
+        <v>-77.34688480000001</v>
       </c>
       <c r="O89">
-        <v>-11.1519428492</v>
+        <v>-11.2926451808</v>
       </c>
       <c r="P89">
-        <v>-65.2312273508</v>
+        <v>-66.05423961920002</v>
       </c>
       <c r="Q89">
-        <v>-72.69122735079999</v>
+        <v>-73.51423961920001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1925867162622599</v>
+        <v>0.2048189426174483</v>
       </c>
       <c r="T89">
-        <v>3.389993447165356</v>
+        <v>3.672492901095803</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01299044391334334</v>
+        <v>0.0128428252325099</v>
       </c>
       <c r="W89">
-        <v>0.2327368533252336</v>
+        <v>0.2327716618101742</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08897564324207763</v>
+        <v>0.08796455638705403</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8751,22 +8751,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2294173355070471</v>
+        <v>0.2313173355070471</v>
       </c>
       <c r="C90">
-        <v>-312.6506552527269</v>
+        <v>-317.16744880707</v>
       </c>
       <c r="D90">
-        <v>41.96534474727304</v>
+        <v>41.53555119292999</v>
       </c>
       <c r="E90">
-        <v>339.956</v>
+        <v>344.043</v>
       </c>
       <c r="F90">
-        <v>359.656</v>
+        <v>363.743</v>
       </c>
       <c r="G90">
         <v>5.04</v>
@@ -8787,37 +8787,37 @@
         <v>7.46</v>
       </c>
       <c r="M90">
-        <v>84.80688480000001</v>
+        <v>85.77059940000001</v>
       </c>
       <c r="N90">
-        <v>-77.34688480000001</v>
+        <v>-78.31059940000002</v>
       </c>
       <c r="O90">
-        <v>-11.2926451808</v>
+        <v>-11.4333475124</v>
       </c>
       <c r="P90">
-        <v>-66.05423961920002</v>
+        <v>-66.87725188760001</v>
       </c>
       <c r="Q90">
-        <v>-73.51423961920001</v>
+        <v>-74.3372518876</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2048189426174483</v>
+        <v>0.2192752101281254</v>
       </c>
       <c r="T90">
-        <v>3.672492901095803</v>
+        <v>4.006355892104512</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0128428252325099</v>
+        <v>0.01269852382540304</v>
       </c>
       <c r="W90">
-        <v>0.2327716618101742</v>
+        <v>0.23280568808197</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08796455638705403</v>
+        <v>0.08697619058495232</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8833,22 +8833,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2313173355070471</v>
+        <v>0.233217335507047</v>
       </c>
       <c r="C91">
-        <v>-317.16744880707</v>
+        <v>-321.6755280367637</v>
       </c>
       <c r="D91">
-        <v>41.53555119292999</v>
+        <v>41.11447196323628</v>
       </c>
       <c r="E91">
-        <v>344.043</v>
+        <v>348.13</v>
       </c>
       <c r="F91">
-        <v>363.743</v>
+        <v>367.83</v>
       </c>
       <c r="G91">
         <v>5.04</v>
@@ -8869,37 +8869,37 @@
         <v>7.46</v>
       </c>
       <c r="M91">
-        <v>85.77059940000001</v>
+        <v>86.734314</v>
       </c>
       <c r="N91">
-        <v>-78.31059940000002</v>
+        <v>-79.274314</v>
       </c>
       <c r="O91">
-        <v>-11.4333475124</v>
+        <v>-11.574049844</v>
       </c>
       <c r="P91">
-        <v>-66.87725188760001</v>
+        <v>-67.700264156</v>
       </c>
       <c r="Q91">
-        <v>-74.3372518876</v>
+        <v>-75.160264156</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2192752101281254</v>
+        <v>0.2366227311409379</v>
       </c>
       <c r="T91">
-        <v>4.006355892104512</v>
+        <v>4.406991481314964</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01269852382540304</v>
+        <v>0.0125574291162319</v>
       </c>
       <c r="W91">
-        <v>0.23280568808197</v>
+        <v>0.2328389582143925</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08697619058495232</v>
+        <v>0.08600978846734175</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8915,22 +8915,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.233217335507047</v>
+        <v>0.2351173355070471</v>
       </c>
       <c r="C92">
-        <v>-321.6755280367637</v>
+        <v>-326.1751553142443</v>
       </c>
       <c r="D92">
-        <v>41.11447196323628</v>
+        <v>40.70184468575571</v>
       </c>
       <c r="E92">
-        <v>348.13</v>
+        <v>352.217</v>
       </c>
       <c r="F92">
-        <v>367.83</v>
+        <v>371.917</v>
       </c>
       <c r="G92">
         <v>5.04</v>
@@ -8951,37 +8951,37 @@
         <v>7.46</v>
       </c>
       <c r="M92">
-        <v>86.734314</v>
+        <v>87.69802860000001</v>
       </c>
       <c r="N92">
-        <v>-79.274314</v>
+        <v>-80.23802860000002</v>
       </c>
       <c r="O92">
-        <v>-11.574049844</v>
+        <v>-11.7147521756</v>
       </c>
       <c r="P92">
-        <v>-67.700264156</v>
+        <v>-68.52327642440002</v>
       </c>
       <c r="Q92">
-        <v>-75.160264156</v>
+        <v>-75.98327642440002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2366227311409379</v>
+        <v>0.2578252568232643</v>
       </c>
       <c r="T92">
-        <v>4.406991481314964</v>
+        <v>4.896657201461071</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0125574291162319</v>
+        <v>0.0124194353896799</v>
       </c>
       <c r="W92">
-        <v>0.2328389582143925</v>
+        <v>0.2328714971351135</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.08600978846734175</v>
+        <v>0.0850646259567116</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8997,22 +8997,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2351173355070471</v>
+        <v>0.2370173355070471</v>
       </c>
       <c r="C93">
-        <v>-326.1751553142443</v>
+        <v>-330.6665825838633</v>
       </c>
       <c r="D93">
-        <v>40.70184468575571</v>
+        <v>40.2974174161367</v>
       </c>
       <c r="E93">
-        <v>352.217</v>
+        <v>356.304</v>
       </c>
       <c r="F93">
-        <v>371.917</v>
+        <v>376.004</v>
       </c>
       <c r="G93">
         <v>5.04</v>
@@ -9033,37 +9033,37 @@
         <v>7.46</v>
       </c>
       <c r="M93">
-        <v>87.69802860000001</v>
+        <v>88.6617432</v>
       </c>
       <c r="N93">
-        <v>-80.23802860000002</v>
+        <v>-81.20174320000001</v>
       </c>
       <c r="O93">
-        <v>-11.7147521756</v>
+        <v>-11.8554545072</v>
       </c>
       <c r="P93">
-        <v>-68.52327642440002</v>
+        <v>-69.34628869280002</v>
       </c>
       <c r="Q93">
-        <v>-75.98327642440002</v>
+        <v>-76.80628869280001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2578252568232643</v>
+        <v>0.2843284139261725</v>
       </c>
       <c r="T93">
-        <v>4.896657201461071</v>
+        <v>5.508739351643707</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0124194353896799</v>
+        <v>0.0122844415267486</v>
       </c>
       <c r="W93">
-        <v>0.2328714971351135</v>
+        <v>0.2329033286879927</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.0850646259567116</v>
+        <v>0.08414001045718211</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9079,22 +9079,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2370173355070471</v>
+        <v>0.2389173355070471</v>
       </c>
       <c r="C94">
-        <v>-330.6665825838633</v>
+        <v>-335.1500518748756</v>
       </c>
       <c r="D94">
-        <v>40.2974174161367</v>
+        <v>39.9009481251244</v>
       </c>
       <c r="E94">
-        <v>356.304</v>
+        <v>360.391</v>
       </c>
       <c r="F94">
-        <v>376.004</v>
+        <v>380.091</v>
       </c>
       <c r="G94">
         <v>5.04</v>
@@ -9115,37 +9115,37 @@
         <v>7.46</v>
       </c>
       <c r="M94">
-        <v>88.6617432</v>
+        <v>89.62545780000001</v>
       </c>
       <c r="N94">
-        <v>-81.20174320000001</v>
+        <v>-82.16545780000001</v>
       </c>
       <c r="O94">
-        <v>-11.8554545072</v>
+        <v>-11.9961568388</v>
       </c>
       <c r="P94">
-        <v>-69.34628869280002</v>
+        <v>-70.16930096120001</v>
       </c>
       <c r="Q94">
-        <v>-76.80628869280001</v>
+        <v>-77.6293009612</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2843284139261725</v>
+        <v>0.3184039016299115</v>
       </c>
       <c r="T94">
-        <v>5.508739351643707</v>
+        <v>6.295702116164238</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0122844415267486</v>
+        <v>0.01215235075764377</v>
       </c>
       <c r="W94">
-        <v>0.2329033286879927</v>
+        <v>0.2329344756913476</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08414001045718211</v>
+        <v>0.08323527916194362</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9161,22 +9161,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2389173355070471</v>
+        <v>0.240817335507047</v>
       </c>
       <c r="C95">
-        <v>-335.1500518748756</v>
+        <v>-339.6257957844394</v>
       </c>
       <c r="D95">
-        <v>39.9009481251244</v>
+        <v>39.51220421556056</v>
       </c>
       <c r="E95">
-        <v>360.391</v>
+        <v>364.478</v>
       </c>
       <c r="F95">
-        <v>380.091</v>
+        <v>384.178</v>
       </c>
       <c r="G95">
         <v>5.04</v>
@@ -9197,37 +9197,37 @@
         <v>7.46</v>
       </c>
       <c r="M95">
-        <v>89.62545780000001</v>
+        <v>90.58917240000001</v>
       </c>
       <c r="N95">
-        <v>-82.16545780000001</v>
+        <v>-83.12917240000002</v>
       </c>
       <c r="O95">
-        <v>-11.9961568388</v>
+        <v>-12.1368591704</v>
       </c>
       <c r="P95">
-        <v>-70.16930096120001</v>
+        <v>-70.99231322960001</v>
       </c>
       <c r="Q95">
-        <v>-77.6293009612</v>
+        <v>-78.45231322960001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3184039016299115</v>
+        <v>0.3638378852348967</v>
       </c>
       <c r="T95">
-        <v>6.295702116164238</v>
+        <v>7.344985802191611</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01215235075764377</v>
+        <v>0.01202307043043479</v>
       </c>
       <c r="W95">
-        <v>0.2329344756913476</v>
+        <v>0.2329649599925035</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.08323527916194362</v>
+        <v>0.08234979746873139</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9243,22 +9243,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.240817335507047</v>
+        <v>0.2427173355070471</v>
       </c>
       <c r="C96">
-        <v>-339.6257957844394</v>
+        <v>-344.0940379326549</v>
       </c>
       <c r="D96">
-        <v>39.51220421556056</v>
+        <v>39.1309620673451</v>
       </c>
       <c r="E96">
-        <v>364.478</v>
+        <v>368.5650000000001</v>
       </c>
       <c r="F96">
-        <v>384.178</v>
+        <v>388.265</v>
       </c>
       <c r="G96">
         <v>5.04</v>
@@ -9279,37 +9279,37 @@
         <v>7.46</v>
       </c>
       <c r="M96">
-        <v>90.58917240000001</v>
+        <v>91.55288700000001</v>
       </c>
       <c r="N96">
-        <v>-83.12917240000002</v>
+        <v>-84.09288700000002</v>
       </c>
       <c r="O96">
-        <v>-12.1368591704</v>
+        <v>-12.277561502</v>
       </c>
       <c r="P96">
-        <v>-70.99231322960001</v>
+        <v>-71.81532549800002</v>
       </c>
       <c r="Q96">
-        <v>-78.45231322960001</v>
+        <v>-79.27532549800002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3638378852348967</v>
+        <v>0.4274454622818763</v>
       </c>
       <c r="T96">
-        <v>7.344985802191611</v>
+        <v>8.813982962629938</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01202307043043479</v>
+        <v>0.01189651179432495</v>
       </c>
       <c r="W96">
-        <v>0.2329649599925035</v>
+        <v>0.2329948025188982</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.08234979746873139</v>
+        <v>0.08148295749537637</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9325,22 +9325,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2427173355070471</v>
+        <v>0.2446173355070471</v>
       </c>
       <c r="C97">
-        <v>-344.0940379326549</v>
+        <v>-348.5549933915104</v>
       </c>
       <c r="D97">
-        <v>39.1309620673451</v>
+        <v>38.75700660848966</v>
       </c>
       <c r="E97">
-        <v>368.5650000000001</v>
+        <v>372.652</v>
       </c>
       <c r="F97">
-        <v>388.265</v>
+        <v>392.352</v>
       </c>
       <c r="G97">
         <v>5.04</v>
@@ -9361,37 +9361,37 @@
         <v>7.46</v>
       </c>
       <c r="M97">
-        <v>91.55288700000001</v>
+        <v>92.51660160000002</v>
       </c>
       <c r="N97">
-        <v>-84.09288700000002</v>
+        <v>-85.05660160000002</v>
       </c>
       <c r="O97">
-        <v>-12.277561502</v>
+        <v>-12.4182638336</v>
       </c>
       <c r="P97">
-        <v>-71.81532549800002</v>
+        <v>-72.63833776640001</v>
       </c>
       <c r="Q97">
-        <v>-79.27532549800002</v>
+        <v>-80.09833776640001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4274454622818763</v>
+        <v>0.5228568278523457</v>
       </c>
       <c r="T97">
-        <v>8.813982962629938</v>
+        <v>11.01747870328743</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01189651179432495</v>
+        <v>0.0117725897964674</v>
       </c>
       <c r="W97">
-        <v>0.2329948025188982</v>
+        <v>0.233024023325993</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08148295749537637</v>
+        <v>0.08063417668813277</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9407,22 +9407,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2446173355070471</v>
+        <v>0.246517335507047</v>
       </c>
       <c r="C98">
-        <v>-348.5549933915103</v>
+        <v>-353.0088690894669</v>
       </c>
       <c r="D98">
-        <v>38.75700660848966</v>
+        <v>38.39013091053307</v>
       </c>
       <c r="E98">
-        <v>372.652</v>
+        <v>376.739</v>
       </c>
       <c r="F98">
-        <v>392.352</v>
+        <v>396.439</v>
       </c>
       <c r="G98">
         <v>5.04</v>
@@ -9443,37 +9443,37 @@
         <v>7.46</v>
       </c>
       <c r="M98">
-        <v>92.5166016</v>
+        <v>93.48031619999999</v>
       </c>
       <c r="N98">
-        <v>-85.05660160000001</v>
+        <v>-86.0203162</v>
       </c>
       <c r="O98">
-        <v>-12.4182638336</v>
+        <v>-12.5589661652</v>
       </c>
       <c r="P98">
-        <v>-72.63833776640001</v>
+        <v>-73.46135003479999</v>
       </c>
       <c r="Q98">
-        <v>-80.09833776640001</v>
+        <v>-80.92135003479999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5228568278523443</v>
+        <v>0.6818757704697924</v>
       </c>
       <c r="T98">
-        <v>11.0174787032874</v>
+        <v>14.6899716043832</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0117725897964674</v>
+        <v>0.01165122289134918</v>
       </c>
       <c r="W98">
-        <v>0.233024023325993</v>
+        <v>0.2330526416422199</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08063417668813289</v>
+        <v>0.07980289651609029</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9489,22 +9489,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.246517335507047</v>
+        <v>0.2484173355070471</v>
       </c>
       <c r="C99">
-        <v>-353.0088690894669</v>
+        <v>-357.4558641932791</v>
       </c>
       <c r="D99">
-        <v>38.39013091053307</v>
+        <v>38.03013580672089</v>
       </c>
       <c r="E99">
-        <v>376.739</v>
+        <v>380.826</v>
       </c>
       <c r="F99">
-        <v>396.439</v>
+        <v>400.526</v>
       </c>
       <c r="G99">
         <v>5.04</v>
@@ -9525,37 +9525,37 @@
         <v>7.46</v>
       </c>
       <c r="M99">
-        <v>93.48031619999999</v>
+        <v>94.44403079999999</v>
       </c>
       <c r="N99">
-        <v>-86.0203162</v>
+        <v>-86.9840308</v>
       </c>
       <c r="O99">
-        <v>-12.5589661652</v>
+        <v>-12.6996684968</v>
       </c>
       <c r="P99">
-        <v>-73.46135003479999</v>
+        <v>-74.2843623032</v>
       </c>
       <c r="Q99">
-        <v>-80.92135003479999</v>
+        <v>-81.74436230319999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6818757704697924</v>
+        <v>0.9999136557046888</v>
       </c>
       <c r="T99">
-        <v>14.6899716043832</v>
+        <v>22.0349574065748</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01165122289134918</v>
+        <v>0.01153233286184562</v>
       </c>
       <c r="W99">
-        <v>0.2330526416422199</v>
+        <v>0.2330806759111768</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07980289651609029</v>
+        <v>0.07898858124551789</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9571,22 +9571,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2484173355070471</v>
+        <v>0.2503173355070471</v>
       </c>
       <c r="C100">
-        <v>-357.4558641932791</v>
+        <v>-361.8961704685326</v>
       </c>
       <c r="D100">
-        <v>38.03013580672089</v>
+        <v>37.67682953146738</v>
       </c>
       <c r="E100">
-        <v>380.826</v>
+        <v>384.913</v>
       </c>
       <c r="F100">
-        <v>400.526</v>
+        <v>404.613</v>
       </c>
       <c r="G100">
         <v>5.04</v>
@@ -9607,37 +9607,37 @@
         <v>7.46</v>
       </c>
       <c r="M100">
-        <v>94.44403079999999</v>
+        <v>95.40774540000001</v>
       </c>
       <c r="N100">
-        <v>-86.9840308</v>
+        <v>-87.94774540000002</v>
       </c>
       <c r="O100">
-        <v>-12.6996684968</v>
+        <v>-12.8403708284</v>
       </c>
       <c r="P100">
-        <v>-74.2843623032</v>
+        <v>-75.10737457160002</v>
       </c>
       <c r="Q100">
-        <v>-81.74436230319999</v>
+        <v>-82.56737457160001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9999136557046888</v>
+        <v>1.954027311409378</v>
       </c>
       <c r="T100">
-        <v>22.0349574065748</v>
+        <v>44.0699148131496</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01153233286184562</v>
+        <v>0.01141584465111991</v>
       </c>
       <c r="W100">
-        <v>0.2330806759111768</v>
+        <v>0.2331081438312659</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9645,91 +9645,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07898858124551789</v>
+        <v>0.07819071678849243</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2503173355070471</v>
-      </c>
-      <c r="C101">
-        <v>-361.8961704685326</v>
-      </c>
-      <c r="D101">
-        <v>37.67682953146738</v>
-      </c>
-      <c r="E101">
-        <v>384.913</v>
-      </c>
-      <c r="F101">
-        <v>404.613</v>
-      </c>
-      <c r="G101">
-        <v>5.04</v>
-      </c>
-      <c r="H101">
-        <v>389</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-7.46</v>
-      </c>
-      <c r="L101">
-        <v>7.46</v>
-      </c>
-      <c r="M101">
-        <v>95.40774540000001</v>
-      </c>
-      <c r="N101">
-        <v>-87.94774540000002</v>
-      </c>
-      <c r="O101">
-        <v>-12.8403708284</v>
-      </c>
-      <c r="P101">
-        <v>-75.10737457160002</v>
-      </c>
-      <c r="Q101">
-        <v>-82.56737457160001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.954027311409378</v>
-      </c>
-      <c r="T101">
-        <v>44.0699148131496</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01141584465111991</v>
-      </c>
-      <c r="W101">
-        <v>0.2331081438312659</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07819071678849243</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
